--- a/RiscISAv1.1 .xlsx
+++ b/RiscISAv1.1 .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37B2EDC-9252-4530-A3ED-6DE11B8C1FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C648284-904B-4481-BEB2-E744D3363285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="454" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="454" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruction format" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="452">
   <si>
     <t>bit0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -503,14 +503,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>易变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>op0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1061,10 +1053,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>立即数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1697,6 +1685,44 @@
   </si>
   <si>
     <t>cpyfvg.mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>[4]</t>
+  </si>
+  <si>
+    <t>[5]</t>
+  </si>
+  <si>
+    <t>[6]</t>
+  </si>
+  <si>
+    <t>[7]</t>
+  </si>
+  <si>
+    <t>PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临界区</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2140,7 +2166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2249,11 +2275,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2306,6 +2329,7 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3001,13 +3025,13 @@
     </row>
     <row r="17" spans="2:25" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="44" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="14"/>
@@ -3021,7 +3045,7 @@
     </row>
     <row r="18" spans="2:25" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="45" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C18" s="46"/>
       <c r="D18" s="46"/>
@@ -3038,7 +3062,7 @@
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>50</v>
@@ -3047,10 +3071,10 @@
         <v>49</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.2">
@@ -3116,19 +3140,19 @@
       <c r="D22" s="46"/>
       <c r="E22" s="46"/>
       <c r="F22" s="44" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K22" s="29"/>
       <c r="L22" s="14"/>
@@ -3152,13 +3176,13 @@
       <c r="D23" s="46"/>
       <c r="E23" s="46"/>
       <c r="F23" s="47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
       <c r="J23" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K23" s="29"/>
       <c r="L23" s="14"/>
@@ -3180,7 +3204,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="K24" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>51</v>
@@ -3192,13 +3216,13 @@
         <v>49</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.2">
@@ -3282,49 +3306,49 @@
     </row>
     <row r="27" spans="2:25" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="D27" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="E27" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="F27" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="G27" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="F27" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="G27" s="44" t="s">
-        <v>271</v>
-      </c>
       <c r="H27" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I27" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="J27" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="K27" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="M27" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="N27" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="P27" s="44" t="s">
         <v>256</v>
-      </c>
-      <c r="J27" s="44" t="s">
-        <v>255</v>
-      </c>
-      <c r="K27" s="44" t="s">
-        <v>254</v>
-      </c>
-      <c r="L27" s="44" t="s">
-        <v>252</v>
-      </c>
-      <c r="M27" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="N27" s="44" t="s">
-        <v>250</v>
-      </c>
-      <c r="O27" s="44" t="s">
-        <v>249</v>
-      </c>
-      <c r="P27" s="44" t="s">
-        <v>258</v>
       </c>
       <c r="Q27" s="29"/>
       <c r="R27" s="14"/>
@@ -3354,37 +3378,37 @@
       <c r="D28" s="46"/>
       <c r="E28" s="46"/>
       <c r="F28" s="44" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H28" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I28" s="44" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J28" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K28" s="44" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L28" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M28" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N28" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O28" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P28" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q28" s="29"/>
       <c r="R28" s="14"/>
@@ -3414,25 +3438,25 @@
       <c r="H29" s="48"/>
       <c r="I29" s="48"/>
       <c r="J29" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K29" s="44" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L29" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M29" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N29" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O29" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P29" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q29" s="29"/>
       <c r="R29" s="14"/>
@@ -3468,13 +3492,13 @@
       <c r="L30" s="50"/>
       <c r="M30" s="50"/>
       <c r="N30" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O30" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P30" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q30" s="25"/>
       <c r="R30" s="26"/>
@@ -3492,31 +3516,31 @@
     </row>
     <row r="31" spans="2:25" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B31" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="46"/>
       <c r="E31" s="46"/>
       <c r="F31" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G31" s="48"/>
       <c r="H31" s="48"/>
       <c r="I31" s="48"/>
       <c r="J31" s="49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K31" s="50"/>
       <c r="L31" s="50"/>
       <c r="M31" s="50"/>
       <c r="N31" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O31" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P31" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q31" s="21"/>
       <c r="R31" s="28"/>
@@ -3545,31 +3569,31 @@
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="T32" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="R32" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="S32" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="T32" s="8" t="s">
-        <v>362</v>
-      </c>
       <c r="U32" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="V32" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="W32" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="V32" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="W32" s="8" t="s">
-        <v>361</v>
-      </c>
       <c r="X32" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.2">
@@ -3677,70 +3701,70 @@
     </row>
     <row r="35" spans="2:33" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="D35" s="44" t="s">
         <v>259</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="E35" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="F35" s="44" t="s">
         <v>261</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="G35" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="F35" s="44" t="s">
+      <c r="H35" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="G35" s="44" t="s">
+      <c r="I35" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="J35" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="I35" s="44" t="s">
+      <c r="K35" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="J35" s="44" t="s">
+      <c r="L35" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="K35" s="44" t="s">
+      <c r="M35" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="L35" s="44" t="s">
+      <c r="N35" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="M35" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="N35" s="44" t="s">
-        <v>271</v>
-      </c>
       <c r="O35" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P35" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q35" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="R35" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="S35" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="T35" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="U35" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="V35" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="W35" s="44" t="s">
         <v>256</v>
-      </c>
-      <c r="Q35" s="44" t="s">
-        <v>255</v>
-      </c>
-      <c r="R35" s="44" t="s">
-        <v>254</v>
-      </c>
-      <c r="S35" s="44" t="s">
-        <v>252</v>
-      </c>
-      <c r="T35" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="U35" s="44" t="s">
-        <v>250</v>
-      </c>
-      <c r="V35" s="44" t="s">
-        <v>249</v>
-      </c>
-      <c r="W35" s="44" t="s">
-        <v>258</v>
       </c>
       <c r="X35" s="29"/>
       <c r="Y35" s="14"/>
@@ -3773,58 +3797,58 @@
       <c r="D36" s="46"/>
       <c r="E36" s="46"/>
       <c r="F36" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="H36" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="G36" s="44" t="s">
+      <c r="I36" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="H36" s="44" t="s">
+      <c r="J36" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="I36" s="44" t="s">
+      <c r="K36" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="J36" s="44" t="s">
+      <c r="L36" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="K36" s="44" t="s">
+      <c r="M36" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="L36" s="44" t="s">
+      <c r="N36" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="M36" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="N36" s="44" t="s">
-        <v>271</v>
-      </c>
       <c r="O36" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P36" s="44" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q36" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R36" s="44" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="S36" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="T36" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U36" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="V36" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W36" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="X36" s="29"/>
       <c r="Y36" s="14"/>
@@ -3855,46 +3879,46 @@
       <c r="H37" s="48"/>
       <c r="I37" s="48"/>
       <c r="J37" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="K37" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="L37" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="K37" s="44" t="s">
+      <c r="M37" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="L37" s="44" t="s">
+      <c r="N37" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="M37" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="N37" s="44" t="s">
-        <v>271</v>
-      </c>
       <c r="O37" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P37" s="44" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q37" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R37" s="44" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="S37" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="T37" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U37" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="V37" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W37" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="X37" s="29"/>
       <c r="Y37" s="14"/>
@@ -3931,34 +3955,34 @@
       <c r="L38" s="50"/>
       <c r="M38" s="50"/>
       <c r="N38" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O38" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P38" s="44" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q38" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R38" s="44" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="S38" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="T38" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U38" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="V38" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W38" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="X38" s="25"/>
       <c r="Y38" s="26"/>
@@ -3977,52 +4001,52 @@
     </row>
     <row r="39" spans="2:33" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B39" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="46"/>
       <c r="E39" s="46"/>
       <c r="F39" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G39" s="48"/>
       <c r="H39" s="48"/>
       <c r="I39" s="48"/>
       <c r="J39" s="49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K39" s="50"/>
       <c r="L39" s="50"/>
       <c r="M39" s="50"/>
       <c r="N39" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O39" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P39" s="44" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q39" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R39" s="44" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="S39" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="T39" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U39" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="V39" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W39" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="X39" s="21"/>
       <c r="Y39" s="28"/>
@@ -4059,34 +4083,34 @@
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y40" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="Z40" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="AA40" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="Y40" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z40" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="AA40" s="8" t="s">
+      <c r="AB40" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="AC40" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD40" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="AB40" s="8" t="s">
+      <c r="AE40" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="AC40" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="AD40" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="AE40" s="8" t="s">
-        <v>361</v>
-      </c>
       <c r="AF40" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AG40" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4111,193 +4135,172 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="D2" s="55" t="s">
-        <v>287</v>
-      </c>
-      <c r="F2" s="59" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>163</v>
+        <v>283</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>284</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>138</v>
+        <v>62</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="34" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" s="52" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51"/>
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F16" s="51"/>
       <c r="G16" s="51"/>
@@ -4309,16 +4312,16 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F17" s="51"/>
       <c r="G17" s="51"/>
@@ -4330,16 +4333,16 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>284</v>
+        <v>96</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>285</v>
+        <v>102</v>
       </c>
       <c r="E18" s="52" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F18" s="51"/>
       <c r="G18" s="51"/>
@@ -4351,43 +4354,64 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>242</v>
+        <v>441</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>103</v>
+        <v>282</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>76</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="52" t="s">
+      <c r="C22" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="E22" s="52" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4396,15 +4420,15 @@
         <v>79</v>
       </c>
       <c r="E24" s="52" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="34" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E26" s="52" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
@@ -4414,10 +4438,10 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D29" s="34" t="s">
         <v>138</v>
@@ -4431,18 +4455,32 @@
         <v>122</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
+      <c r="F30" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G30" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H30" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I30" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J30" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K30" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L30" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="34" t="s">
@@ -4452,18 +4490,32 @@
         <v>123</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="F31" s="56"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="56"/>
+      <c r="F31" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G31" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H31" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I31" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J31" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K31" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L31" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="34" t="s">
@@ -4473,18 +4525,32 @@
         <v>124</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="F32" s="56"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="56"/>
+      <c r="F32" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G32" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H32" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I32" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J32" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K32" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L32" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="34" t="s">
@@ -4494,18 +4560,32 @@
         <v>125</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="F33" s="56"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="56"/>
+      <c r="F33" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G33" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H33" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I33" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J33" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K33" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L33" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="34" t="s">
@@ -4515,18 +4595,32 @@
         <v>126</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="E34" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="E34" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58"/>
+      <c r="F34" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G34" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H34" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I34" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J34" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K34" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L34" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="34" t="s">
@@ -4536,18 +4630,32 @@
         <v>127</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="E35" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
+      <c r="F35" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G35" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H35" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I35" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J35" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K35" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L35" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="34" t="s">
@@ -4559,16 +4667,30 @@
       <c r="D36" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="E36" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="58"/>
+      <c r="E36" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="F36" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G36" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H36" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I36" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J36" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K36" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L36" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="34" t="s">
@@ -4578,18 +4700,32 @@
         <v>129</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" s="54" t="s">
-        <v>244</v>
-      </c>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="58"/>
+        <v>152</v>
+      </c>
+      <c r="E37" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="F37" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G37" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H37" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I37" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J37" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K37" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L37" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="34" t="s">
@@ -4599,18 +4735,32 @@
         <v>130</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" s="54" t="s">
-        <v>245</v>
-      </c>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
+        <v>153</v>
+      </c>
+      <c r="E38" s="55" t="s">
+        <v>243</v>
+      </c>
+      <c r="F38" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G38" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H38" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I38" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J38" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K38" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L38" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="34" t="s">
@@ -4620,18 +4770,32 @@
         <v>131</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="E39" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58"/>
+        <v>154</v>
+      </c>
+      <c r="E39" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G39" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H39" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I39" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J39" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K39" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L39" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" s="34" t="s">
@@ -4641,18 +4805,32 @@
         <v>132</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" s="54" t="s">
-        <v>238</v>
-      </c>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
+        <v>155</v>
+      </c>
+      <c r="E40" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="F40" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G40" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H40" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I40" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J40" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K40" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L40" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="34" t="s">
@@ -4662,18 +4840,32 @@
         <v>133</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="E41" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
+        <v>156</v>
+      </c>
+      <c r="E41" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="F41" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G41" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H41" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I41" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J41" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K41" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L41" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="34" t="s">
@@ -4683,18 +4875,32 @@
         <v>134</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" s="54" t="s">
-        <v>240</v>
-      </c>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="58"/>
+        <v>157</v>
+      </c>
+      <c r="E42" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="F42" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G42" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H42" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I42" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J42" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K42" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L42" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="34" t="s">
@@ -4704,18 +4910,32 @@
         <v>135</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="E43" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="E43" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="58"/>
-      <c r="K43" s="58"/>
-      <c r="L43" s="58"/>
+      <c r="F43" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G43" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H43" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I43" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J43" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K43" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L43" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B44" s="34" t="s">
@@ -4725,18 +4945,32 @@
         <v>136</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E44" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="58"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="58"/>
+      <c r="F44" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G44" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H44" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I44" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J44" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K44" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L44" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="34" t="s">
@@ -4746,18 +4980,32 @@
         <v>137</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="E45" s="54" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
+      <c r="F45" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="G45" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H45" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="I45" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="J45" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="K45" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="L45" s="74" t="s">
+        <v>448</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4767,7 +5015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EF87AE-E07A-4F2D-9B14-1FA4C48C4D5A}">
-  <dimension ref="B2:E11"/>
+  <dimension ref="B2:E12"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="34"/>
@@ -4775,61 +5023,69 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B2" s="34" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" s="34" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" s="34" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D6" s="34" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" s="34" t="s">
-        <v>190</v>
+        <v>449</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>297</v>
+        <v>449</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B11" s="34" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>297</v>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -4848,15 +5104,15 @@
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B2" s="34" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>25</v>
@@ -4952,15 +5208,15 @@
         <v>1</v>
       </c>
       <c r="AG3" s="34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B4" s="35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="40"/>
@@ -4977,77 +5233,77 @@
       <c r="P4" s="40"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="S4" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="T4" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="S4" s="37" t="s">
+      <c r="U4" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="T4" s="37" t="s">
+      <c r="V4" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="U4" s="37" t="s">
+      <c r="W4" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="V4" s="37" t="s">
+      <c r="X4" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="W4" s="37" t="s">
+      <c r="Y4" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="X4" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y4" s="38" t="s">
-        <v>185</v>
-      </c>
       <c r="Z4" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA4" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB4" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="AA4" s="37" t="s">
+      <c r="AC4" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD4" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE4" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AF4" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG4" s="38" t="s">
         <v>171</v>
-      </c>
-      <c r="AB4" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="AC4" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="AD4" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE4" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="AF4" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="AG4" s="38" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B5" s="34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R5" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Z5" s="34" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
@@ -5082,34 +5338,34 @@
       <c r="AD9" s="37"/>
       <c r="AE9" s="37"/>
       <c r="AF9" s="35" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG9" s="35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B11" s="34" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="34" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>25</v>
@@ -5205,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="AG19" s="34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.2">
@@ -5239,35 +5495,35 @@
       <c r="AC20" s="37"/>
       <c r="AD20" s="37"/>
       <c r="AE20" s="38" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AF20" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG20" s="38"/>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="AE21" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AF21" s="34" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>25</v>
@@ -5363,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.2">
@@ -5398,29 +5654,29 @@
       <c r="AD24" s="37"/>
       <c r="AE24" s="38"/>
       <c r="AF24" s="36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG24" s="38"/>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="AF25" s="34" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="34" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>25</v>
@@ -5516,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="AG27" s="34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.2">
@@ -5589,50 +5845,50 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B32" s="34" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="34" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" s="34" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" s="34" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" s="34" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B39" s="34" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -5663,543 +5919,543 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I2" s="30" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="Q2" s="30" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B3" s="70" t="s">
-        <v>409</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>411</v>
-      </c>
-      <c r="F3" s="72" t="s">
-        <v>410</v>
-      </c>
-      <c r="I3" s="61" t="s">
-        <v>272</v>
-      </c>
-      <c r="J3" s="64" t="s">
+      <c r="B3" s="67" t="s">
+        <v>406</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>408</v>
+      </c>
+      <c r="F3" s="69" t="s">
+        <v>407</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="J3" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="62" t="s">
-        <v>273</v>
-      </c>
-      <c r="L3" s="64" t="s">
+      <c r="K3" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="L3" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="M3" s="62" t="s">
+      <c r="M3" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="N3" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="O3" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q3" s="61" t="s">
-        <v>272</v>
-      </c>
-      <c r="R3" s="64" t="s">
+      <c r="N3" s="61" t="s">
+        <v>321</v>
+      </c>
+      <c r="O3" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q3" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="R3" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="S3" s="62" t="s">
-        <v>273</v>
-      </c>
-      <c r="T3" s="64" t="s">
+      <c r="S3" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="T3" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="V3" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="W3" s="63" t="s">
-        <v>300</v>
+      <c r="V3" s="61" t="s">
+        <v>321</v>
+      </c>
+      <c r="W3" s="60" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I4" s="41"/>
-      <c r="J4" s="60"/>
+      <c r="J4" s="57"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="60" t="s">
-        <v>325</v>
+      <c r="L4" s="57" t="s">
+        <v>322</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="N4" s="60" t="s">
-        <v>327</v>
+        <v>323</v>
+      </c>
+      <c r="N4" s="57" t="s">
+        <v>324</v>
       </c>
       <c r="O4" s="43"/>
       <c r="Q4" s="41"/>
-      <c r="R4" s="60"/>
+      <c r="R4" s="57"/>
       <c r="S4" s="42"/>
-      <c r="T4" s="60" t="s">
-        <v>325</v>
+      <c r="T4" s="57" t="s">
+        <v>322</v>
       </c>
       <c r="U4" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="V4" s="60" t="s">
         <v>323</v>
       </c>
+      <c r="V4" s="57" t="s">
+        <v>320</v>
+      </c>
       <c r="W4" s="43"/>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="K5" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L5" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N5" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" s="65" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q5" s="69" t="s">
+      <c r="J5" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="K5" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L5" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" s="62" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q5" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="R5" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="S5" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T5" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U5" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V5" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W5" s="65" t="s">
-        <v>339</v>
+      <c r="R5" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="S5" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T5" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W5" s="62" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B6" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="K6" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L6" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M6" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O6" s="65" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="S6" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T6" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U6" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V6" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W6" s="65" t="s">
-        <v>347</v>
+        <v>420</v>
+      </c>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="K6" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L6" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="62" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="S6" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T6" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U6" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W6" s="62" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B7" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>60</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E7" s="31" t="s">
         <v>58</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G7" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="K7" s="67" t="s">
         <v>300</v>
       </c>
-      <c r="I7" s="69"/>
-      <c r="J7" s="70" t="s">
+      <c r="L7" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" s="62" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="S7" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T7" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U7" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V7" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W7" s="62" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B8" s="66" t="s">
+        <v>418</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="I8" s="66"/>
+      <c r="J8" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="K8" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="62" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="S8" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V8" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" s="62" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B9" s="66"/>
+      <c r="C9" s="67" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="I9" s="66"/>
+      <c r="J9" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="K9" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="62" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="S9" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V9" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" s="62" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B10" s="66"/>
+      <c r="C10" s="67" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="I10" s="66"/>
+      <c r="J10" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="K7" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L7" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O7" s="65" t="s">
+      <c r="K10" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="70" t="s">
+      <c r="Q10" s="66"/>
+      <c r="R10" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="S7" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T7" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U7" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V7" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W7" s="65" t="s">
+      <c r="S10" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V10" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" s="62" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B8" s="69" t="s">
-        <v>421</v>
-      </c>
-      <c r="C8" s="70" t="s">
-        <v>279</v>
-      </c>
-      <c r="D8" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="E8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="65" t="s">
-        <v>331</v>
-      </c>
-      <c r="I8" s="69"/>
-      <c r="J8" s="70" t="s">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B11" s="66"/>
+      <c r="C11" s="67" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="62" t="s">
+        <v>333</v>
+      </c>
+      <c r="I11" s="66"/>
+      <c r="J11" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="K8" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="65" t="s">
+      <c r="K11" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11" s="62" t="s">
         <v>342</v>
       </c>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="70" t="s">
+      <c r="Q11" s="66"/>
+      <c r="R11" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="S8" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V8" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W8" s="65" t="s">
+      <c r="S11" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" s="62" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B9" s="69"/>
-      <c r="C9" s="70" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="E9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="65" t="s">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B12" s="66"/>
+      <c r="C12" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="E12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>438</v>
+      </c>
+      <c r="I12" s="66"/>
+      <c r="J12" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="K12" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O12" s="62" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="S12" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="T12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="U12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W12" s="62" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B13" s="66"/>
+      <c r="C13" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="62" t="s">
         <v>274</v>
-      </c>
-      <c r="I9" s="69"/>
-      <c r="J9" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="K9" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O9" s="65" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="S9" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V9" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W9" s="65" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B10" s="69"/>
-      <c r="C10" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="D10" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="E10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="65" t="s">
-        <v>275</v>
-      </c>
-      <c r="I10" s="69"/>
-      <c r="J10" s="70" t="s">
-        <v>308</v>
-      </c>
-      <c r="K10" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O10" s="65" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="70" t="s">
-        <v>308</v>
-      </c>
-      <c r="S10" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W10" s="65" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B11" s="69"/>
-      <c r="C11" s="70" t="s">
-        <v>282</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="E11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>336</v>
-      </c>
-      <c r="I11" s="69"/>
-      <c r="J11" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="K11" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O11" s="65" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q11" s="69"/>
-      <c r="R11" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="S11" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V11" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W11" s="65" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B12" s="69"/>
-      <c r="C12" s="70" t="s">
-        <v>413</v>
-      </c>
-      <c r="D12" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="65" t="s">
-        <v>441</v>
-      </c>
-      <c r="I12" s="69"/>
-      <c r="J12" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="K12" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="L12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="M12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O12" s="65" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="S12" s="70" t="s">
-        <v>332</v>
-      </c>
-      <c r="T12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V12" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W12" s="65" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B13" s="69"/>
-      <c r="C13" s="70" t="s">
-        <v>414</v>
-      </c>
-      <c r="D13" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="E13" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="65" t="s">
-        <v>276</v>
       </c>
       <c r="I13" s="32"/>
       <c r="J13" s="30" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K13" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L13" s="30" t="s">
         <v>57</v>
@@ -6213,10 +6469,10 @@
       <c r="O13" s="33"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="30" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="S13" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T13" s="30" t="s">
         <v>57</v>
@@ -6232,10 +6488,10 @@
     <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B14" s="32"/>
       <c r="C14" s="30" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E14" s="30" t="s">
         <v>57</v>
@@ -6246,10 +6502,10 @@
       <c r="G14" s="33"/>
       <c r="I14" s="32"/>
       <c r="J14" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L14" s="30" t="s">
         <v>57</v>
@@ -6263,10 +6519,10 @@
       <c r="O14" s="33"/>
       <c r="Q14" s="32"/>
       <c r="R14" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="S14" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T14" s="30" t="s">
         <v>57</v>
@@ -6282,10 +6538,10 @@
     <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B15" s="32"/>
       <c r="C15" s="30" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E15" s="30" t="s">
         <v>57</v>
@@ -6296,10 +6552,10 @@
       <c r="G15" s="33"/>
       <c r="I15" s="32"/>
       <c r="J15" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K15" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L15" s="30" t="s">
         <v>57</v>
@@ -6313,10 +6569,10 @@
       <c r="O15" s="33"/>
       <c r="Q15" s="32"/>
       <c r="R15" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="S15" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T15" s="30" t="s">
         <v>57</v>
@@ -6334,10 +6590,10 @@
       <c r="G16" s="33"/>
       <c r="I16" s="32"/>
       <c r="J16" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L16" s="30" t="s">
         <v>57</v>
@@ -6351,10 +6607,10 @@
       <c r="O16" s="33"/>
       <c r="Q16" s="32"/>
       <c r="R16" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T16" s="30" t="s">
         <v>57</v>
@@ -6368,30 +6624,30 @@
       <c r="W16" s="33"/>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B17" s="69" t="s">
-        <v>422</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>279</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>420</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="65" t="s">
+      <c r="B17" s="66" t="s">
+        <v>419</v>
+      </c>
+      <c r="C17" s="67" t="s">
         <v>277</v>
+      </c>
+      <c r="D17" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="67" t="s">
+        <v>417</v>
+      </c>
+      <c r="F17" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>275</v>
       </c>
       <c r="I17" s="32"/>
       <c r="J17" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L17" s="30" t="s">
         <v>57</v>
@@ -6405,10 +6661,10 @@
       <c r="O17" s="33"/>
       <c r="Q17" s="32"/>
       <c r="R17" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T17" s="30" t="s">
         <v>57</v>
@@ -6422,28 +6678,28 @@
       <c r="W17" s="33"/>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B18" s="69"/>
-      <c r="C18" s="70" t="s">
-        <v>280</v>
-      </c>
-      <c r="D18" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="70" t="s">
-        <v>420</v>
-      </c>
-      <c r="F18" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="65" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="67" t="s">
         <v>278</v>
+      </c>
+      <c r="D18" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="67" t="s">
+        <v>417</v>
+      </c>
+      <c r="F18" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="62" t="s">
+        <v>276</v>
       </c>
       <c r="I18" s="32"/>
       <c r="J18" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L18" s="30" t="s">
         <v>57</v>
@@ -6457,10 +6713,10 @@
       <c r="O18" s="33"/>
       <c r="Q18" s="32"/>
       <c r="R18" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="S18" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T18" s="30" t="s">
         <v>57</v>
@@ -6476,13 +6732,13 @@
     <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" s="32"/>
       <c r="C19" s="30" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D19" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>57</v>
@@ -6490,10 +6746,10 @@
       <c r="G19" s="33"/>
       <c r="I19" s="32"/>
       <c r="J19" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L19" s="30" t="s">
         <v>57</v>
@@ -6507,10 +6763,10 @@
       <c r="O19" s="33"/>
       <c r="Q19" s="32"/>
       <c r="R19" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S19" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T19" s="30" t="s">
         <v>57</v>
@@ -6526,13 +6782,13 @@
     <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B20" s="32"/>
       <c r="C20" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D20" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F20" s="30" t="s">
         <v>57</v>
@@ -6540,10 +6796,10 @@
       <c r="G20" s="33"/>
       <c r="I20" s="32"/>
       <c r="J20" s="30" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L20" s="30" t="s">
         <v>57</v>
@@ -6557,10 +6813,10 @@
       <c r="O20" s="33"/>
       <c r="Q20" s="32"/>
       <c r="R20" s="30" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T20" s="30" t="s">
         <v>57</v>
@@ -6576,13 +6832,13 @@
     <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" s="32"/>
       <c r="C21" s="30" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D21" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F21" s="30" t="s">
         <v>57</v>
@@ -6596,101 +6852,101 @@
     <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" s="32"/>
       <c r="C22" s="30" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D22" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>57</v>
       </c>
       <c r="G22" s="33"/>
-      <c r="I22" s="69" t="s">
+      <c r="I22" s="66" t="s">
+        <v>296</v>
+      </c>
+      <c r="J22" s="67" t="s">
         <v>299</v>
       </c>
-      <c r="J22" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="K22" s="70" t="s">
-        <v>320</v>
-      </c>
-      <c r="L22" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M22" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O22" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q22" s="69" t="s">
+      <c r="K22" s="67" t="s">
+        <v>317</v>
+      </c>
+      <c r="L22" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O22" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q22" s="66" t="s">
+        <v>296</v>
+      </c>
+      <c r="R22" s="67" t="s">
         <v>299</v>
       </c>
-      <c r="R22" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="S22" s="70" t="s">
-        <v>333</v>
-      </c>
-      <c r="T22" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U22" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="V22" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W22" s="65" t="s">
-        <v>387</v>
+      <c r="S22" s="67" t="s">
+        <v>330</v>
+      </c>
+      <c r="T22" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U22" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V22" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W22" s="62" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" s="32"/>
       <c r="C23" s="30" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D23" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F23" s="30" t="s">
         <v>57</v>
       </c>
       <c r="G23" s="33"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="K23" s="70" t="s">
-        <v>320</v>
-      </c>
-      <c r="L23" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="N23" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O23" s="65" t="s">
-        <v>355</v>
+      <c r="I23" s="66"/>
+      <c r="J23" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="K23" s="67" t="s">
+        <v>317</v>
+      </c>
+      <c r="L23" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="N23" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O23" s="62" t="s">
+        <v>352</v>
       </c>
       <c r="Q23" s="32"/>
       <c r="R23" s="30" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="S23" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T23" s="30" t="s">
         <v>61</v>
@@ -6706,13 +6962,13 @@
     <row r="24" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B24" s="41"/>
       <c r="C24" s="42" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F24" s="42" t="s">
         <v>57</v>
@@ -6720,10 +6976,10 @@
       <c r="G24" s="43"/>
       <c r="I24" s="32"/>
       <c r="J24" s="30" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L24" s="30" t="s">
         <v>61</v>
@@ -6737,10 +6993,10 @@
       <c r="O24" s="33"/>
       <c r="Q24" s="32"/>
       <c r="R24" s="30" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="S24" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T24" s="30" t="s">
         <v>61</v>
@@ -6756,10 +7012,10 @@
     <row r="25" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I25" s="32"/>
       <c r="J25" s="30" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L25" s="30" t="s">
         <v>61</v>
@@ -6773,10 +7029,10 @@
       <c r="O25" s="33"/>
       <c r="Q25" s="32"/>
       <c r="R25" s="30" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T25" s="30" t="s">
         <v>61</v>
@@ -6792,10 +7048,10 @@
     <row r="26" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I26" s="32"/>
       <c r="J26" s="30" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L26" s="30" t="s">
         <v>61</v>
@@ -6809,10 +7065,10 @@
       <c r="O26" s="33"/>
       <c r="Q26" s="32"/>
       <c r="R26" s="30" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="S26" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T26" s="30" t="s">
         <v>61</v>
@@ -6828,10 +7084,10 @@
     <row r="27" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I27" s="32"/>
       <c r="J27" s="30" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K27" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L27" s="30" t="s">
         <v>61</v>
@@ -6845,10 +7101,10 @@
       <c r="O27" s="33"/>
       <c r="Q27" s="32"/>
       <c r="R27" s="30" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="S27" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T27" s="30" t="s">
         <v>61</v>
@@ -6863,14 +7119,14 @@
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B28" s="30" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="I28" s="32"/>
       <c r="J28" s="30" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K28" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>61</v>
@@ -6884,10 +7140,10 @@
       <c r="O28" s="33"/>
       <c r="Q28" s="32"/>
       <c r="R28" s="30" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="S28" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T28" s="30" t="s">
         <v>61</v>
@@ -6902,13 +7158,13 @@
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B29" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>60</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E29" s="31" t="s">
         <v>58</v>
@@ -6917,14 +7173,14 @@
         <v>59</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="30" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L29" s="30" t="s">
         <v>61</v>
@@ -6938,10 +7194,10 @@
       <c r="O29" s="33"/>
       <c r="Q29" s="32"/>
       <c r="R29" s="30" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="S29" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T29" s="30" t="s">
         <v>61</v>
@@ -6955,30 +7211,30 @@
       <c r="W29" s="33"/>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B30" s="69" t="s">
-        <v>417</v>
-      </c>
-      <c r="C30" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>439</v>
-      </c>
-      <c r="E30" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" s="65" t="s">
-        <v>412</v>
+      <c r="B30" s="66" t="s">
+        <v>414</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="D30" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="E30" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="62" t="s">
+        <v>409</v>
       </c>
       <c r="I30" s="32"/>
       <c r="J30" s="30" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K30" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L30" s="30" t="s">
         <v>61</v>
@@ -6992,10 +7248,10 @@
       <c r="O30" s="33"/>
       <c r="Q30" s="32"/>
       <c r="R30" s="30" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="S30" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T30" s="30" t="s">
         <v>61</v>
@@ -7009,28 +7265,28 @@
       <c r="W30" s="33"/>
     </row>
     <row r="31" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B31" s="69"/>
-      <c r="C31" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>439</v>
-      </c>
-      <c r="E31" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31" s="65" t="s">
-        <v>337</v>
+      <c r="B31" s="66"/>
+      <c r="C31" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="D31" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="E31" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="62" t="s">
+        <v>334</v>
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L31" s="30" t="s">
         <v>61</v>
@@ -7044,10 +7300,10 @@
       <c r="O31" s="33"/>
       <c r="Q31" s="32"/>
       <c r="R31" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="S31" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T31" s="30" t="s">
         <v>61</v>
@@ -7061,28 +7317,28 @@
       <c r="W31" s="33"/>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B32" s="69"/>
-      <c r="C32" s="70" t="s">
-        <v>305</v>
-      </c>
-      <c r="D32" s="70" t="s">
-        <v>439</v>
-      </c>
-      <c r="E32" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32" s="65" t="s">
-        <v>429</v>
+      <c r="B32" s="66"/>
+      <c r="C32" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="D32" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="E32" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="62" t="s">
+        <v>426</v>
       </c>
       <c r="I32" s="32"/>
       <c r="J32" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K32" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L32" s="30" t="s">
         <v>61</v>
@@ -7096,10 +7352,10 @@
       <c r="O32" s="33"/>
       <c r="Q32" s="32"/>
       <c r="R32" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="S32" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T32" s="30" t="s">
         <v>61</v>
@@ -7113,28 +7369,28 @@
       <c r="W32" s="33"/>
     </row>
     <row r="33" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B33" s="69"/>
-      <c r="C33" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="D33" s="70" t="s">
-        <v>439</v>
-      </c>
-      <c r="E33" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G33" s="65" t="s">
-        <v>430</v>
+      <c r="B33" s="66"/>
+      <c r="C33" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="D33" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="E33" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G33" s="62" t="s">
+        <v>427</v>
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K33" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L33" s="30" t="s">
         <v>61</v>
@@ -7148,10 +7404,10 @@
       <c r="O33" s="33"/>
       <c r="Q33" s="32"/>
       <c r="R33" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="S33" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T33" s="30" t="s">
         <v>61</v>
@@ -7167,10 +7423,10 @@
     <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B34" s="32"/>
       <c r="C34" s="30" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E34" s="30" t="s">
         <v>61</v>
@@ -7181,10 +7437,10 @@
       <c r="G34" s="33"/>
       <c r="I34" s="32"/>
       <c r="J34" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K34" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L34" s="30" t="s">
         <v>61</v>
@@ -7198,10 +7454,10 @@
       <c r="O34" s="33"/>
       <c r="Q34" s="32"/>
       <c r="R34" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="S34" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T34" s="30" t="s">
         <v>61</v>
@@ -7217,10 +7473,10 @@
     <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B35" s="32"/>
       <c r="C35" s="30" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E35" s="30" t="s">
         <v>61</v>
@@ -7231,10 +7487,10 @@
       <c r="G35" s="33"/>
       <c r="I35" s="32"/>
       <c r="J35" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K35" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L35" s="30" t="s">
         <v>61</v>
@@ -7248,10 +7504,10 @@
       <c r="O35" s="33"/>
       <c r="Q35" s="32"/>
       <c r="R35" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="S35" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T35" s="30" t="s">
         <v>61</v>
@@ -7267,10 +7523,10 @@
     <row r="36" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B36" s="32"/>
       <c r="C36" s="30" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E36" s="30" t="s">
         <v>61</v>
@@ -7281,10 +7537,10 @@
       <c r="G36" s="33"/>
       <c r="I36" s="32"/>
       <c r="J36" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="K36" s="30" t="s">
         <v>317</v>
-      </c>
-      <c r="K36" s="30" t="s">
-        <v>320</v>
       </c>
       <c r="L36" s="30" t="s">
         <v>61</v>
@@ -7298,10 +7554,10 @@
       <c r="O36" s="33"/>
       <c r="Q36" s="32"/>
       <c r="R36" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S36" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T36" s="30" t="s">
         <v>61</v>
@@ -7317,10 +7573,10 @@
     <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="32"/>
       <c r="C37" s="30" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>61</v>
@@ -7331,10 +7587,10 @@
       <c r="G37" s="33"/>
       <c r="I37" s="32"/>
       <c r="J37" s="30" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L37" s="30" t="s">
         <v>61</v>
@@ -7348,10 +7604,10 @@
       <c r="O37" s="33"/>
       <c r="Q37" s="32"/>
       <c r="R37" s="30" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S37" s="30" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="T37" s="30" t="s">
         <v>61</v>
@@ -7367,10 +7623,10 @@
     <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B38" s="32"/>
       <c r="C38" s="30" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E38" s="30" t="s">
         <v>61</v>
@@ -7387,10 +7643,10 @@
     <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B39" s="32"/>
       <c r="C39" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>61</v>
@@ -7399,56 +7655,56 @@
         <v>57</v>
       </c>
       <c r="G39" s="33"/>
-      <c r="I39" s="69" t="s">
-        <v>301</v>
-      </c>
-      <c r="J39" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="K39" s="70" t="s">
-        <v>321</v>
-      </c>
-      <c r="L39" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M39" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="N39" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O39" s="65" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q39" s="69" t="s">
-        <v>301</v>
-      </c>
-      <c r="R39" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="S39" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T39" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U39" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V39" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W39" s="65" t="s">
-        <v>369</v>
+      <c r="I39" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="J39" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="K39" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="L39" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="N39" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O39" s="62" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q39" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="R39" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="S39" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T39" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U39" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V39" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W39" s="62" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B40" s="32"/>
       <c r="C40" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E40" s="30" t="s">
         <v>61</v>
@@ -7457,52 +7713,52 @@
         <v>57</v>
       </c>
       <c r="G40" s="33"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="K40" s="70" t="s">
-        <v>321</v>
-      </c>
-      <c r="L40" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M40" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="N40" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O40" s="65" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q40" s="69"/>
-      <c r="R40" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="S40" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T40" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U40" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V40" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W40" s="65" t="s">
-        <v>370</v>
+      <c r="I40" s="66"/>
+      <c r="J40" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="K40" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="L40" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M40" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="N40" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O40" s="62" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="S40" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T40" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U40" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V40" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W40" s="62" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B41" s="32"/>
       <c r="C41" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E41" s="30" t="s">
         <v>61</v>
@@ -7511,52 +7767,52 @@
         <v>57</v>
       </c>
       <c r="G41" s="33"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="70" t="s">
-        <v>305</v>
-      </c>
-      <c r="K41" s="70" t="s">
-        <v>321</v>
-      </c>
-      <c r="L41" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M41" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="N41" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O41" s="65" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="70" t="s">
-        <v>305</v>
-      </c>
-      <c r="S41" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T41" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U41" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V41" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W41" s="65" t="s">
-        <v>371</v>
+      <c r="I41" s="66"/>
+      <c r="J41" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="K41" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="L41" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M41" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="N41" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O41" s="62" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q41" s="66"/>
+      <c r="R41" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="S41" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T41" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U41" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V41" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W41" s="62" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B42" s="32"/>
       <c r="C42" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E42" s="30" t="s">
         <v>61</v>
@@ -7565,106 +7821,106 @@
         <v>57</v>
       </c>
       <c r="G42" s="33"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="K42" s="70" t="s">
-        <v>321</v>
-      </c>
-      <c r="L42" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M42" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="N42" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="O42" s="65" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q42" s="69"/>
-      <c r="R42" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="S42" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T42" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U42" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V42" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W42" s="65" t="s">
-        <v>372</v>
+      <c r="I42" s="66"/>
+      <c r="J42" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="K42" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="L42" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M42" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="N42" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="O42" s="62" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="S42" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T42" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U42" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V42" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W42" s="62" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B43" s="32"/>
       <c r="C43" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D43" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G43" s="33"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="69" t="s">
+        <v>304</v>
+      </c>
+      <c r="K43" s="69" t="s">
+        <v>318</v>
+      </c>
+      <c r="L43" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="M43" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="N43" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="O43" s="63" t="s">
         <v>439</v>
       </c>
-      <c r="E43" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F43" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G43" s="33"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="72" t="s">
-        <v>307</v>
-      </c>
-      <c r="K43" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="L43" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="M43" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="N43" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="O43" s="66" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q43" s="69"/>
-      <c r="R43" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="S43" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T43" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U43" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V43" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W43" s="65" t="s">
-        <v>373</v>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="S43" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T43" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U43" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V43" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W43" s="62" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B44" s="32"/>
       <c r="C44" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E44" s="30" t="s">
         <v>61</v>
@@ -7673,496 +7929,496 @@
         <v>57</v>
       </c>
       <c r="G44" s="33"/>
-      <c r="I44" s="73"/>
-      <c r="J44" s="72" t="s">
-        <v>308</v>
-      </c>
-      <c r="K44" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="L44" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="M44" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="N44" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="O44" s="66" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q44" s="69"/>
-      <c r="R44" s="70" t="s">
-        <v>308</v>
-      </c>
-      <c r="S44" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T44" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U44" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V44" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W44" s="65" t="s">
-        <v>374</v>
+      <c r="I44" s="70"/>
+      <c r="J44" s="69" t="s">
+        <v>305</v>
+      </c>
+      <c r="K44" s="69" t="s">
+        <v>318</v>
+      </c>
+      <c r="L44" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="N44" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="O44" s="63" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="S44" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T44" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U44" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V44" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W44" s="62" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B45" s="32"/>
       <c r="C45" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F45" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" s="33"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="69" t="s">
+        <v>306</v>
+      </c>
+      <c r="K45" s="69" t="s">
         <v>318</v>
       </c>
-      <c r="D45" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F45" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G45" s="33"/>
-      <c r="I45" s="73"/>
-      <c r="J45" s="72" t="s">
-        <v>309</v>
-      </c>
-      <c r="K45" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="L45" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="M45" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="N45" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="O45" s="66" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q45" s="69"/>
-      <c r="R45" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="S45" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T45" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U45" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V45" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W45" s="65" t="s">
-        <v>375</v>
+      <c r="L45" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="M45" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="N45" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="O45" s="63" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="67" t="s">
+        <v>306</v>
+      </c>
+      <c r="S45" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T45" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U45" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V45" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W45" s="62" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B46" s="32"/>
       <c r="G46" s="33"/>
-      <c r="I46" s="73"/>
-      <c r="J46" s="72" t="s">
-        <v>310</v>
-      </c>
-      <c r="K46" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="L46" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="M46" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="N46" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="O46" s="66" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q46" s="69"/>
-      <c r="R46" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="S46" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T46" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U46" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V46" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W46" s="65" t="s">
-        <v>376</v>
+      <c r="I46" s="70"/>
+      <c r="J46" s="69" t="s">
+        <v>307</v>
+      </c>
+      <c r="K46" s="69" t="s">
+        <v>318</v>
+      </c>
+      <c r="L46" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="M46" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="N46" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="O46" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q46" s="66"/>
+      <c r="R46" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="S46" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T46" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U46" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V46" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W46" s="62" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B47" s="69" t="s">
-        <v>418</v>
-      </c>
-      <c r="C47" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="D47" s="70" t="s">
-        <v>440</v>
-      </c>
-      <c r="E47" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="G47" s="65" t="s">
-        <v>366</v>
+      <c r="B47" s="66" t="s">
+        <v>415</v>
+      </c>
+      <c r="C47" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="D47" s="67" t="s">
+        <v>437</v>
+      </c>
+      <c r="E47" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F47" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="G47" s="62" t="s">
+        <v>363</v>
       </c>
       <c r="I47" s="32"/>
       <c r="J47" s="30" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K47" s="30" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L47" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M47" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N47" s="30" t="s">
         <v>57</v>
       </c>
       <c r="O47" s="33"/>
-      <c r="Q47" s="69"/>
-      <c r="R47" s="70" t="s">
-        <v>311</v>
-      </c>
-      <c r="S47" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T47" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U47" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V47" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W47" s="65" t="s">
-        <v>377</v>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="S47" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T47" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U47" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V47" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W47" s="62" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B48" s="74"/>
-      <c r="C48" s="71" t="s">
-        <v>304</v>
-      </c>
-      <c r="D48" s="71" t="s">
-        <v>440</v>
-      </c>
-      <c r="E48" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="F48" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="G48" s="67" t="s">
-        <v>367</v>
+      <c r="B48" s="71"/>
+      <c r="C48" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D48" s="68" t="s">
+        <v>437</v>
+      </c>
+      <c r="E48" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="G48" s="64" t="s">
+        <v>364</v>
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K48" s="30" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L48" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M48" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N48" s="30" t="s">
         <v>57</v>
       </c>
       <c r="O48" s="33"/>
-      <c r="Q48" s="69"/>
-      <c r="R48" s="70" t="s">
-        <v>312</v>
-      </c>
-      <c r="S48" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="T48" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="U48" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="V48" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="W48" s="65" t="s">
-        <v>378</v>
+      <c r="Q48" s="66"/>
+      <c r="R48" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="S48" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="T48" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="U48" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="V48" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W48" s="62" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="49" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B49" s="69"/>
-      <c r="C49" s="70" t="s">
-        <v>305</v>
-      </c>
-      <c r="D49" s="70" t="s">
-        <v>440</v>
-      </c>
-      <c r="E49" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F49" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="G49" s="65" t="s">
-        <v>393</v>
+      <c r="B49" s="66"/>
+      <c r="C49" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="D49" s="67" t="s">
+        <v>437</v>
+      </c>
+      <c r="E49" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F49" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="G49" s="62" t="s">
+        <v>390</v>
       </c>
       <c r="I49" s="32"/>
       <c r="J49" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K49" s="30" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L49" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M49" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N49" s="30" t="s">
         <v>57</v>
       </c>
       <c r="O49" s="33"/>
-      <c r="Q49" s="74"/>
-      <c r="R49" s="71" t="s">
-        <v>313</v>
-      </c>
-      <c r="S49" s="71" t="s">
-        <v>334</v>
-      </c>
-      <c r="T49" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="U49" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="V49" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="W49" s="67" t="s">
-        <v>398</v>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="68" t="s">
+        <v>310</v>
+      </c>
+      <c r="S49" s="68" t="s">
+        <v>331</v>
+      </c>
+      <c r="T49" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="U49" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="V49" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="W49" s="64" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="50" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B50" s="69"/>
-      <c r="C50" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="D50" s="70" t="s">
-        <v>440</v>
-      </c>
-      <c r="E50" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F50" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="G50" s="65" t="s">
-        <v>388</v>
+      <c r="B50" s="66"/>
+      <c r="C50" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="D50" s="67" t="s">
+        <v>437</v>
+      </c>
+      <c r="E50" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F50" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="G50" s="62" t="s">
+        <v>385</v>
       </c>
       <c r="I50" s="32"/>
       <c r="J50" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K50" s="30" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L50" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M50" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N50" s="30" t="s">
         <v>57</v>
       </c>
       <c r="O50" s="33"/>
-      <c r="Q50" s="74"/>
-      <c r="R50" s="71" t="s">
-        <v>314</v>
-      </c>
-      <c r="S50" s="71" t="s">
-        <v>334</v>
-      </c>
-      <c r="T50" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="U50" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="V50" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="W50" s="67" t="s">
-        <v>399</v>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="S50" s="68" t="s">
+        <v>331</v>
+      </c>
+      <c r="T50" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="U50" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="V50" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" s="64" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="51" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B51" s="69"/>
-      <c r="C51" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="D51" s="70" t="s">
-        <v>440</v>
-      </c>
-      <c r="E51" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="F51" s="70" t="s">
-        <v>328</v>
-      </c>
-      <c r="G51" s="65" t="s">
-        <v>389</v>
+      <c r="B51" s="66"/>
+      <c r="C51" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="D51" s="67" t="s">
+        <v>437</v>
+      </c>
+      <c r="E51" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F51" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="G51" s="62" t="s">
+        <v>386</v>
       </c>
       <c r="I51" s="32"/>
       <c r="J51" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K51" s="30" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L51" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M51" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N51" s="30" t="s">
         <v>57</v>
       </c>
       <c r="O51" s="33"/>
-      <c r="Q51" s="73"/>
-      <c r="R51" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="S51" s="72" t="s">
-        <v>334</v>
-      </c>
-      <c r="T51" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="U51" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="V51" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="W51" s="66" t="s">
-        <v>400</v>
+      <c r="Q51" s="70"/>
+      <c r="R51" s="69" t="s">
+        <v>312</v>
+      </c>
+      <c r="S51" s="69" t="s">
+        <v>331</v>
+      </c>
+      <c r="T51" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="U51" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="V51" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" s="63" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="52" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B52" s="74"/>
-      <c r="C52" s="71" t="s">
-        <v>308</v>
-      </c>
-      <c r="D52" s="71" t="s">
-        <v>440</v>
-      </c>
-      <c r="E52" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="F52" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="G52" s="67" t="s">
-        <v>390</v>
+      <c r="B52" s="71"/>
+      <c r="C52" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D52" s="68" t="s">
+        <v>437</v>
+      </c>
+      <c r="E52" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="G52" s="64" t="s">
+        <v>387</v>
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L52" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M52" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N52" s="30" t="s">
         <v>57</v>
       </c>
       <c r="O52" s="33"/>
-      <c r="Q52" s="73"/>
-      <c r="R52" s="72" t="s">
-        <v>316</v>
-      </c>
-      <c r="S52" s="72" t="s">
-        <v>334</v>
-      </c>
-      <c r="T52" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="U52" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="V52" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="W52" s="66" t="s">
-        <v>401</v>
+      <c r="Q52" s="70"/>
+      <c r="R52" s="69" t="s">
+        <v>313</v>
+      </c>
+      <c r="S52" s="69" t="s">
+        <v>331</v>
+      </c>
+      <c r="T52" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="U52" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="V52" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" s="63" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="53" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B53" s="74"/>
-      <c r="C53" s="71" t="s">
-        <v>309</v>
-      </c>
-      <c r="D53" s="71" t="s">
-        <v>440</v>
-      </c>
-      <c r="E53" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="F53" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="G53" s="67" t="s">
-        <v>391</v>
+      <c r="B53" s="71"/>
+      <c r="C53" s="68" t="s">
+        <v>306</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>437</v>
+      </c>
+      <c r="E53" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="F53" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="G53" s="64" t="s">
+        <v>388</v>
       </c>
       <c r="I53" s="32"/>
       <c r="J53" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K53" s="30" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L53" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M53" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N53" s="30" t="s">
         <v>57</v>
@@ -8170,16 +8426,16 @@
       <c r="O53" s="33"/>
       <c r="Q53" s="32"/>
       <c r="R53" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S53" s="30" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="T53" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U53" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="V53" s="30" t="s">
         <v>57</v>
@@ -8187,34 +8443,34 @@
       <c r="W53" s="33"/>
     </row>
     <row r="54" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B54" s="73"/>
-      <c r="C54" s="72" t="s">
-        <v>310</v>
-      </c>
-      <c r="D54" s="72" t="s">
-        <v>440</v>
-      </c>
-      <c r="E54" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="F54" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="G54" s="66" t="s">
-        <v>402</v>
+      <c r="B54" s="70"/>
+      <c r="C54" s="69" t="s">
+        <v>307</v>
+      </c>
+      <c r="D54" s="69" t="s">
+        <v>437</v>
+      </c>
+      <c r="E54" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="G54" s="63" t="s">
+        <v>399</v>
       </c>
       <c r="I54" s="32"/>
       <c r="J54" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="K54" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="K54" s="30" t="s">
-        <v>321</v>
-      </c>
       <c r="L54" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M54" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N54" s="30" t="s">
         <v>57</v>
@@ -8222,16 +8478,16 @@
       <c r="O54" s="33"/>
       <c r="Q54" s="32"/>
       <c r="R54" s="30" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S54" s="30" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="T54" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U54" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="V54" s="30" t="s">
         <v>57</v>
@@ -8239,21 +8495,21 @@
       <c r="W54" s="33"/>
     </row>
     <row r="55" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B55" s="73"/>
-      <c r="C55" s="72" t="s">
-        <v>311</v>
-      </c>
-      <c r="D55" s="72" t="s">
-        <v>440</v>
-      </c>
-      <c r="E55" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="F55" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="G55" s="66" t="s">
-        <v>403</v>
+      <c r="B55" s="70"/>
+      <c r="C55" s="69" t="s">
+        <v>308</v>
+      </c>
+      <c r="D55" s="69" t="s">
+        <v>437</v>
+      </c>
+      <c r="E55" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="G55" s="63" t="s">
+        <v>400</v>
       </c>
       <c r="I55" s="32"/>
       <c r="O55" s="33"/>
@@ -8263,7 +8519,7 @@
     <row r="56" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B56" s="32"/>
       <c r="C56" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>57</v>
@@ -8272,56 +8528,56 @@
         <v>61</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G56" s="33"/>
-      <c r="I56" s="69" t="s">
+      <c r="I56" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="J56" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="K56" s="67" t="s">
         <v>319</v>
       </c>
-      <c r="J56" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="K56" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L56" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M56" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N56" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O56" s="65" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q56" s="73" t="s">
-        <v>319</v>
-      </c>
-      <c r="R56" s="72" t="s">
-        <v>302</v>
-      </c>
-      <c r="S56" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="T56" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="U56" s="72" t="s">
-        <v>329</v>
-      </c>
-      <c r="V56" s="72" t="s">
-        <v>330</v>
-      </c>
-      <c r="W56" s="66" t="s">
-        <v>404</v>
+      <c r="L56" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M56" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N56" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O56" s="62" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q56" s="70" t="s">
+        <v>316</v>
+      </c>
+      <c r="R56" s="69" t="s">
+        <v>299</v>
+      </c>
+      <c r="S56" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="T56" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="U56" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="V56" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="W56" s="63" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="57" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B57" s="32"/>
       <c r="C57" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D57" s="30" t="s">
         <v>57</v>
@@ -8330,52 +8586,52 @@
         <v>61</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G57" s="33"/>
-      <c r="I57" s="69"/>
-      <c r="J57" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="K57" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L57" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M57" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N57" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O57" s="65" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q57" s="73"/>
-      <c r="R57" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="S57" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="T57" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="U57" s="72" t="s">
-        <v>329</v>
-      </c>
-      <c r="V57" s="72" t="s">
-        <v>330</v>
-      </c>
-      <c r="W57" s="66" t="s">
-        <v>405</v>
+      <c r="I57" s="66"/>
+      <c r="J57" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="K57" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L57" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M57" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N57" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O57" s="62" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q57" s="70"/>
+      <c r="R57" s="69" t="s">
+        <v>301</v>
+      </c>
+      <c r="S57" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="T57" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="U57" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="V57" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="W57" s="63" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B58" s="32"/>
       <c r="C58" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D58" s="30" t="s">
         <v>57</v>
@@ -8384,52 +8640,52 @@
         <v>61</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G58" s="33"/>
-      <c r="I58" s="69"/>
-      <c r="J58" s="70" t="s">
-        <v>305</v>
-      </c>
-      <c r="K58" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L58" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M58" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N58" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O58" s="65" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q58" s="73"/>
-      <c r="R58" s="72" t="s">
-        <v>305</v>
-      </c>
-      <c r="S58" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="T58" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="U58" s="72" t="s">
-        <v>329</v>
-      </c>
-      <c r="V58" s="72" t="s">
-        <v>330</v>
-      </c>
-      <c r="W58" s="66" t="s">
-        <v>406</v>
+      <c r="I58" s="66"/>
+      <c r="J58" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="K58" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L58" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M58" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N58" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O58" s="62" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q58" s="70"/>
+      <c r="R58" s="69" t="s">
+        <v>302</v>
+      </c>
+      <c r="S58" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="T58" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="U58" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="V58" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="W58" s="63" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="59" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B59" s="32"/>
       <c r="C59" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>57</v>
@@ -8438,52 +8694,52 @@
         <v>61</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G59" s="33"/>
-      <c r="I59" s="69"/>
-      <c r="J59" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="K59" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L59" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M59" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N59" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O59" s="65" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q59" s="73"/>
-      <c r="R59" s="72" t="s">
-        <v>306</v>
-      </c>
-      <c r="S59" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="T59" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="U59" s="72" t="s">
-        <v>329</v>
-      </c>
-      <c r="V59" s="72" t="s">
-        <v>330</v>
-      </c>
-      <c r="W59" s="66" t="s">
-        <v>407</v>
+      <c r="I59" s="66"/>
+      <c r="J59" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="K59" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L59" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M59" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N59" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O59" s="62" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q59" s="70"/>
+      <c r="R59" s="69" t="s">
+        <v>303</v>
+      </c>
+      <c r="S59" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="T59" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="U59" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="V59" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="W59" s="63" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="60" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B60" s="32"/>
       <c r="C60" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D60" s="30" t="s">
         <v>57</v>
@@ -8492,52 +8748,52 @@
         <v>61</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G60" s="33"/>
-      <c r="I60" s="69"/>
-      <c r="J60" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="K60" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L60" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M60" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N60" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O60" s="65" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q60" s="73"/>
-      <c r="R60" s="72" t="s">
-        <v>307</v>
-      </c>
-      <c r="S60" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="T60" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="U60" s="72" t="s">
-        <v>329</v>
-      </c>
-      <c r="V60" s="72" t="s">
-        <v>330</v>
-      </c>
-      <c r="W60" s="66" t="s">
-        <v>408</v>
+      <c r="I60" s="66"/>
+      <c r="J60" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="K60" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L60" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M60" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N60" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O60" s="62" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q60" s="70"/>
+      <c r="R60" s="69" t="s">
+        <v>304</v>
+      </c>
+      <c r="S60" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="T60" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="U60" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="V60" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="W60" s="63" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="61" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B61" s="32"/>
       <c r="C61" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D61" s="30" t="s">
         <v>57</v>
@@ -8546,50 +8802,50 @@
         <v>61</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G61" s="33"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="70" t="s">
-        <v>308</v>
-      </c>
-      <c r="K61" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L61" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M61" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N61" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O61" s="65" t="s">
-        <v>382</v>
+      <c r="I61" s="66"/>
+      <c r="J61" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="K61" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L61" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M61" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N61" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O61" s="62" t="s">
+        <v>379</v>
       </c>
       <c r="Q61" s="32"/>
       <c r="R61" s="30" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="S61" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T61" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U61" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V61" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W61" s="33"/>
     </row>
     <row r="62" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B62" s="41"/>
       <c r="C62" s="42" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D62" s="42" t="s">
         <v>57</v>
@@ -8598,385 +8854,385 @@
         <v>61</v>
       </c>
       <c r="F62" s="42" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G62" s="43"/>
-      <c r="I62" s="69"/>
-      <c r="J62" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="K62" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L62" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M62" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N62" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O62" s="65" t="s">
-        <v>392</v>
+      <c r="I62" s="66"/>
+      <c r="J62" s="67" t="s">
+        <v>306</v>
+      </c>
+      <c r="K62" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L62" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M62" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N62" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O62" s="62" t="s">
+        <v>389</v>
       </c>
       <c r="Q62" s="32"/>
       <c r="R62" s="30" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="S62" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T62" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U62" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V62" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W62" s="33"/>
     </row>
     <row r="63" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="I63" s="69"/>
-      <c r="J63" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="K63" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L63" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M63" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N63" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O63" s="65" t="s">
-        <v>383</v>
+      <c r="I63" s="66"/>
+      <c r="J63" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="K63" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L63" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M63" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N63" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O63" s="62" t="s">
+        <v>380</v>
       </c>
       <c r="Q63" s="32"/>
       <c r="R63" s="30" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="S63" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T63" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U63" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V63" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W63" s="33"/>
     </row>
     <row r="64" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="I64" s="69"/>
-      <c r="J64" s="70" t="s">
-        <v>311</v>
-      </c>
-      <c r="K64" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L64" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M64" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N64" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O64" s="65" t="s">
-        <v>384</v>
+      <c r="I64" s="66"/>
+      <c r="J64" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="K64" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L64" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M64" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N64" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O64" s="62" t="s">
+        <v>381</v>
       </c>
       <c r="Q64" s="32"/>
       <c r="R64" s="30" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="S64" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T64" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U64" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V64" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W64" s="33"/>
     </row>
     <row r="65" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I65" s="69"/>
-      <c r="J65" s="70" t="s">
-        <v>312</v>
-      </c>
-      <c r="K65" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L65" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M65" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N65" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O65" s="65" t="s">
-        <v>434</v>
+      <c r="I65" s="66"/>
+      <c r="J65" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="K65" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L65" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M65" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N65" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O65" s="62" t="s">
+        <v>431</v>
       </c>
       <c r="Q65" s="32"/>
       <c r="R65" s="30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="S65" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T65" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U65" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V65" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W65" s="33"/>
     </row>
     <row r="66" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I66" s="69"/>
-      <c r="J66" s="70" t="s">
-        <v>313</v>
-      </c>
-      <c r="K66" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L66" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M66" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N66" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O66" s="65" t="s">
-        <v>385</v>
+      <c r="I66" s="66"/>
+      <c r="J66" s="67" t="s">
+        <v>310</v>
+      </c>
+      <c r="K66" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L66" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M66" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N66" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O66" s="62" t="s">
+        <v>382</v>
       </c>
       <c r="Q66" s="32"/>
       <c r="R66" s="30" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="S66" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T66" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U66" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V66" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W66" s="33"/>
     </row>
     <row r="67" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I67" s="69"/>
-      <c r="J67" s="70" t="s">
-        <v>314</v>
-      </c>
-      <c r="K67" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L67" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M67" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N67" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O67" s="65" t="s">
-        <v>386</v>
+      <c r="I67" s="66"/>
+      <c r="J67" s="67" t="s">
+        <v>311</v>
+      </c>
+      <c r="K67" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L67" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M67" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N67" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O67" s="62" t="s">
+        <v>383</v>
       </c>
       <c r="Q67" s="32"/>
       <c r="R67" s="30" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="S67" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T67" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U67" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V67" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W67" s="33"/>
     </row>
     <row r="68" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I68" s="69"/>
-      <c r="J68" s="70" t="s">
-        <v>315</v>
-      </c>
-      <c r="K68" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L68" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M68" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N68" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O68" s="65" t="s">
-        <v>394</v>
+      <c r="I68" s="66"/>
+      <c r="J68" s="67" t="s">
+        <v>312</v>
+      </c>
+      <c r="K68" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L68" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M68" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N68" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O68" s="62" t="s">
+        <v>391</v>
       </c>
       <c r="Q68" s="32"/>
       <c r="R68" s="30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="S68" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T68" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U68" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V68" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W68" s="33"/>
     </row>
     <row r="69" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I69" s="69"/>
-      <c r="J69" s="70" t="s">
-        <v>316</v>
-      </c>
-      <c r="K69" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="L69" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="M69" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="N69" s="70" t="s">
-        <v>330</v>
-      </c>
-      <c r="O69" s="65" t="s">
-        <v>396</v>
+      <c r="I69" s="66"/>
+      <c r="J69" s="67" t="s">
+        <v>313</v>
+      </c>
+      <c r="K69" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="L69" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M69" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="N69" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="O69" s="62" t="s">
+        <v>393</v>
       </c>
       <c r="Q69" s="32"/>
       <c r="R69" s="30" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="S69" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T69" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U69" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V69" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W69" s="33"/>
     </row>
     <row r="70" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I70" s="74"/>
-      <c r="J70" s="71" t="s">
-        <v>317</v>
-      </c>
-      <c r="K70" s="71" t="s">
-        <v>322</v>
-      </c>
-      <c r="L70" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="M70" s="71" t="s">
-        <v>329</v>
-      </c>
-      <c r="N70" s="71" t="s">
-        <v>330</v>
-      </c>
-      <c r="O70" s="67" t="s">
-        <v>395</v>
+      <c r="I70" s="71"/>
+      <c r="J70" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="K70" s="68" t="s">
+        <v>319</v>
+      </c>
+      <c r="L70" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="M70" s="68" t="s">
+        <v>326</v>
+      </c>
+      <c r="N70" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="O70" s="64" t="s">
+        <v>392</v>
       </c>
       <c r="Q70" s="32"/>
       <c r="R70" s="30" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S70" s="30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T70" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U70" s="30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V70" s="30" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W70" s="33"/>
     </row>
     <row r="71" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I71" s="75"/>
-      <c r="J71" s="76" t="s">
-        <v>318</v>
-      </c>
-      <c r="K71" s="76" t="s">
-        <v>322</v>
-      </c>
-      <c r="L71" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="M71" s="76" t="s">
-        <v>329</v>
-      </c>
-      <c r="N71" s="76" t="s">
-        <v>330</v>
-      </c>
-      <c r="O71" s="68" t="s">
-        <v>397</v>
+      <c r="I71" s="72"/>
+      <c r="J71" s="73" t="s">
+        <v>315</v>
+      </c>
+      <c r="K71" s="73" t="s">
+        <v>319</v>
+      </c>
+      <c r="L71" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="M71" s="73" t="s">
+        <v>326</v>
+      </c>
+      <c r="N71" s="73" t="s">
+        <v>327</v>
+      </c>
+      <c r="O71" s="65" t="s">
+        <v>394</v>
       </c>
       <c r="Q71" s="41"/>
       <c r="R71" s="42" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S71" s="42" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T71" s="42" t="s">
         <v>61</v>
       </c>
       <c r="U71" s="42" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="V71" s="42" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W71" s="43"/>
     </row>

--- a/RiscISAv1.1 .xlsx
+++ b/RiscISAv1.1 .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036E7E1F-3B4D-447B-AB8A-1A85D31640CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79849496-652C-414E-8799-FB13120F6BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="454" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="453">
   <si>
     <t>bit0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -916,10 +916,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>break</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>psr</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1116,10 +1112,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>scall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>callr.cond</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1739,6 +1731,10 @@
   </si>
   <si>
     <t>popd.mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scall.mode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3051,7 +3047,7 @@
     </row>
     <row r="18" spans="2:25" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="43" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="44"/>
@@ -3068,7 +3064,7 @@
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>50</v>
@@ -3210,7 +3206,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="K24" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>51</v>
@@ -3225,10 +3221,10 @@
         <v>203</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.2">
@@ -3575,28 +3571,28 @@
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="S32" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="T32" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="U32" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="V32" s="8" t="s">
         <v>203</v>
       </c>
       <c r="W32" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="X32" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Y32" s="8" t="s">
         <v>202</v>
@@ -4089,31 +4085,31 @@
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Y40" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="Z40" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AA40" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AB40" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AC40" s="8" t="s">
         <v>203</v>
       </c>
       <c r="AD40" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AE40" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AF40" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG40" s="8" t="s">
         <v>202</v>
@@ -4141,13 +4137,13 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="F2" s="52" t="s">
         <v>256</v>
-      </c>
-      <c r="F2" s="52" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -4244,10 +4240,10 @@
         <v>68</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>68</v>
@@ -4258,10 +4254,10 @@
         <v>69</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E13" s="50" t="s">
         <v>69</v>
@@ -4272,10 +4268,10 @@
         <v>70</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E14" s="50" t="s">
         <v>70</v>
@@ -4286,7 +4282,7 @@
         <v>71</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>87</v>
@@ -4300,7 +4296,7 @@
         <v>72</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>88</v>
@@ -4316,7 +4312,7 @@
         <v>73</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>89</v>
@@ -4332,7 +4328,7 @@
         <v>74</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D18" s="34" t="s">
         <v>90</v>
@@ -4447,10 +4443,10 @@
         <v>100</v>
       </c>
       <c r="F30" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G30" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
@@ -4467,10 +4463,10 @@
         <v>101</v>
       </c>
       <c r="F31" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G31" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
@@ -4487,10 +4483,10 @@
         <v>102</v>
       </c>
       <c r="F32" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G32" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
@@ -4507,10 +4503,10 @@
         <v>103</v>
       </c>
       <c r="F33" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G33" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
@@ -4527,10 +4523,10 @@
         <v>104</v>
       </c>
       <c r="F34" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G34" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
@@ -4538,19 +4534,19 @@
         <v>105</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E35" s="53" t="s">
         <v>105</v>
       </c>
       <c r="F35" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G35" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
@@ -4558,19 +4554,19 @@
         <v>106</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E36" s="53" t="s">
         <v>218</v>
       </c>
       <c r="F36" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G36" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
@@ -4578,19 +4574,19 @@
         <v>107</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E37" s="53" t="s">
         <v>216</v>
       </c>
       <c r="F37" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G37" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
@@ -4598,7 +4594,7 @@
         <v>108</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D38" s="34" t="s">
         <v>87</v>
@@ -4607,10 +4603,10 @@
         <v>217</v>
       </c>
       <c r="F38" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G38" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
@@ -4618,7 +4614,7 @@
         <v>109</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D39" s="34" t="s">
         <v>140</v>
@@ -4627,10 +4623,10 @@
         <v>209</v>
       </c>
       <c r="F39" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G39" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
@@ -4647,10 +4643,10 @@
         <v>210</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G40" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
@@ -4667,10 +4663,10 @@
         <v>211</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G41" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
@@ -4687,10 +4683,10 @@
         <v>212</v>
       </c>
       <c r="F42" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G42" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
@@ -4707,10 +4703,10 @@
         <v>113</v>
       </c>
       <c r="F43" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G43" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
@@ -4721,16 +4717,16 @@
         <v>125</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E44" s="53" t="s">
         <v>114</v>
       </c>
       <c r="F44" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G44" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
@@ -4741,16 +4737,16 @@
         <v>126</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E45" s="53" t="s">
         <v>115</v>
       </c>
       <c r="F45" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G45" s="69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4772,15 +4768,15 @@
         <v>204</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="34" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -4932,19 +4928,19 @@
         <v>100</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D27" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G27" s="71" t="s">
         <v>100</v>
       </c>
       <c r="H27" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I27" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -4952,19 +4948,19 @@
         <v>101</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G28" s="71" t="s">
         <v>101</v>
       </c>
       <c r="H28" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I28" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -4972,19 +4968,19 @@
         <v>102</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G29" s="71" t="s">
         <v>102</v>
       </c>
       <c r="H29" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I29" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -4992,19 +4988,19 @@
         <v>103</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D30" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G30" s="71" t="s">
         <v>103</v>
       </c>
       <c r="H30" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I30" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -5012,19 +5008,19 @@
         <v>104</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D31" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G31" s="71" t="s">
         <v>104</v>
       </c>
       <c r="H31" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I31" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -5032,19 +5028,19 @@
         <v>105</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D32" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G32" s="71" t="s">
         <v>105</v>
       </c>
       <c r="H32" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I32" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
@@ -5052,19 +5048,19 @@
         <v>218</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D33" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G33" s="71" t="s">
         <v>218</v>
       </c>
       <c r="H33" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I33" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
@@ -5072,19 +5068,19 @@
         <v>216</v>
       </c>
       <c r="C34" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D34" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G34" s="71" t="s">
         <v>216</v>
       </c>
       <c r="H34" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I34" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
@@ -5092,19 +5088,19 @@
         <v>217</v>
       </c>
       <c r="C35" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G35" s="70" t="s">
         <v>217</v>
       </c>
       <c r="H35" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I35" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
@@ -5112,19 +5108,19 @@
         <v>209</v>
       </c>
       <c r="C36" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D36" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G36" s="70" t="s">
         <v>209</v>
       </c>
       <c r="H36" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I36" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.2">
@@ -5132,19 +5128,19 @@
         <v>210</v>
       </c>
       <c r="C37" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D37" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G37" s="70" t="s">
         <v>210</v>
       </c>
       <c r="H37" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I37" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
@@ -5152,19 +5148,19 @@
         <v>211</v>
       </c>
       <c r="C38" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G38" s="70" t="s">
         <v>211</v>
       </c>
       <c r="H38" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I38" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.2">
@@ -5172,19 +5168,19 @@
         <v>212</v>
       </c>
       <c r="C39" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D39" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G39" s="70" t="s">
         <v>212</v>
       </c>
       <c r="H39" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I39" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
@@ -5192,19 +5188,19 @@
         <v>113</v>
       </c>
       <c r="C40" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D40" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G40" s="70" t="s">
         <v>113</v>
       </c>
       <c r="H40" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I40" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
@@ -5212,19 +5208,19 @@
         <v>114</v>
       </c>
       <c r="C41" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D41" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G41" s="70" t="s">
         <v>114</v>
       </c>
       <c r="H41" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I41" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.2">
@@ -5232,19 +5228,19 @@
         <v>115</v>
       </c>
       <c r="C42" s="72" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D42" s="72" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G42" s="70" t="s">
         <v>115</v>
       </c>
       <c r="H42" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I42" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -5456,24 +5452,24 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>184</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>40</v>
@@ -5647,13 +5643,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>40</v>
@@ -5777,7 +5773,7 @@
       <c r="AC15" s="75"/>
       <c r="AD15" s="75"/>
       <c r="AE15" s="35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AF15" s="35" t="s">
         <v>197</v>
@@ -5825,7 +5821,7 @@
       <c r="AC17" s="75"/>
       <c r="AD17" s="75"/>
       <c r="AE17" s="35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AF17" s="35" t="s">
         <v>197</v>
@@ -5839,21 +5835,21 @@
         <v>188</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D20" s="34" t="s">
         <v>40</v>
@@ -6016,10 +6012,10 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B23" s="34" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.2">
@@ -6092,24 +6088,24 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D28" s="34" t="s">
         <v>40</v>
@@ -6272,10 +6268,10 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B31" s="34" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.2">
@@ -6639,7 +6635,7 @@
       <c r="AC41" s="37"/>
       <c r="AD41" s="37"/>
       <c r="AE41" s="35" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AF41" s="36" t="s">
         <v>179</v>
@@ -6648,7 +6644,7 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A43" s="34" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>183</v>
@@ -6828,18 +6824,18 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A48" s="34" t="s">
+        <v>416</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="C48" s="34" t="s">
         <v>418</v>
-      </c>
-      <c r="B48" s="34" t="s">
-        <v>419</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>25</v>
@@ -7011,7 +7007,7 @@
         <v>192</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.2">
@@ -7019,7 +7015,7 @@
         <v>193</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.2">
@@ -7027,7 +7023,7 @@
         <v>194</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.2">
@@ -7035,7 +7031,7 @@
         <v>189</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.2">
@@ -7043,7 +7039,7 @@
         <v>190</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.2">
@@ -7051,7 +7047,7 @@
         <v>191</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -7082,21 +7078,21 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I2" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>368</v>
-      </c>
-      <c r="Q2" s="30" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B3" s="64" t="s">
+        <v>351</v>
+      </c>
+      <c r="D3" s="65" t="s">
         <v>353</v>
       </c>
-      <c r="D3" s="65" t="s">
-        <v>355</v>
-      </c>
       <c r="F3" s="66" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I3" s="56" t="s">
         <v>242</v>
@@ -7114,10 +7110,10 @@
         <v>59</v>
       </c>
       <c r="N3" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O3" s="58" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q3" s="56" t="s">
         <v>242</v>
@@ -7135,10 +7131,10 @@
         <v>59</v>
       </c>
       <c r="V3" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="W3" s="58" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="2:23" x14ac:dyDescent="0.2">
@@ -7146,26 +7142,26 @@
       <c r="J4" s="55"/>
       <c r="K4" s="40"/>
       <c r="L4" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="N4" s="55" t="s">
         <v>286</v>
-      </c>
-      <c r="N4" s="55" t="s">
-        <v>287</v>
       </c>
       <c r="O4" s="41"/>
       <c r="Q4" s="39"/>
       <c r="R4" s="55"/>
       <c r="S4" s="40"/>
       <c r="T4" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="U4" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="U4" s="40" t="s">
-        <v>286</v>
-      </c>
       <c r="V4" s="55" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W4" s="41"/>
     </row>
@@ -7174,11 +7170,11 @@
         <v>56</v>
       </c>
       <c r="J5" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="K5" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="K5" s="64" t="s">
-        <v>263</v>
-      </c>
       <c r="L5" s="64" t="s">
         <v>57</v>
       </c>
@@ -7189,16 +7185,16 @@
         <v>57</v>
       </c>
       <c r="O5" s="60" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Q5" s="63" t="s">
         <v>56</v>
       </c>
       <c r="R5" s="64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S5" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T5" s="64" t="s">
         <v>57</v>
@@ -7210,19 +7206,19 @@
         <v>57</v>
       </c>
       <c r="W5" s="60" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B6" s="30" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I6" s="63"/>
       <c r="J6" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K6" s="64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L6" s="64" t="s">
         <v>57</v>
@@ -7234,14 +7230,14 @@
         <v>57</v>
       </c>
       <c r="O6" s="60" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q6" s="63"/>
       <c r="R6" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S6" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T6" s="64" t="s">
         <v>57</v>
@@ -7253,7 +7249,7 @@
         <v>57</v>
       </c>
       <c r="W6" s="60" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
@@ -7270,17 +7266,17 @@
         <v>58</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I7" s="63"/>
       <c r="J7" s="64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K7" s="64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L7" s="64" t="s">
         <v>57</v>
@@ -7292,14 +7288,14 @@
         <v>57</v>
       </c>
       <c r="O7" s="60" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q7" s="63"/>
       <c r="R7" s="64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="S7" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T7" s="64" t="s">
         <v>57</v>
@@ -7311,18 +7307,18 @@
         <v>57</v>
       </c>
       <c r="W7" s="60" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B8" s="63" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D8" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E8" s="64" t="s">
         <v>57</v>
@@ -7331,14 +7327,14 @@
         <v>57</v>
       </c>
       <c r="G8" s="60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I8" s="63"/>
       <c r="J8" s="64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K8" s="64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L8" s="64" t="s">
         <v>57</v>
@@ -7350,14 +7346,14 @@
         <v>57</v>
       </c>
       <c r="O8" s="60" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q8" s="63"/>
       <c r="R8" s="64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S8" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T8" s="64" t="s">
         <v>57</v>
@@ -7369,16 +7365,16 @@
         <v>57</v>
       </c>
       <c r="W8" s="60" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B9" s="63"/>
       <c r="C9" s="64" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E9" s="64" t="s">
         <v>57</v>
@@ -7391,10 +7387,10 @@
       </c>
       <c r="I9" s="63"/>
       <c r="J9" s="64" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K9" s="64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L9" s="64" t="s">
         <v>57</v>
@@ -7406,14 +7402,14 @@
         <v>57</v>
       </c>
       <c r="O9" s="60" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q9" s="63"/>
       <c r="R9" s="64" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="S9" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T9" s="64" t="s">
         <v>57</v>
@@ -7425,16 +7421,16 @@
         <v>57</v>
       </c>
       <c r="W9" s="60" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B10" s="63"/>
       <c r="C10" s="64" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E10" s="64" t="s">
         <v>57</v>
@@ -7447,10 +7443,10 @@
       </c>
       <c r="I10" s="63"/>
       <c r="J10" s="64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K10" s="64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L10" s="64" t="s">
         <v>57</v>
@@ -7462,14 +7458,14 @@
         <v>57</v>
       </c>
       <c r="O10" s="60" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q10" s="63"/>
       <c r="R10" s="64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="S10" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T10" s="64" t="s">
         <v>57</v>
@@ -7481,16 +7477,16 @@
         <v>57</v>
       </c>
       <c r="W10" s="60" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B11" s="63"/>
       <c r="C11" s="64" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D11" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E11" s="64" t="s">
         <v>57</v>
@@ -7499,14 +7495,14 @@
         <v>57</v>
       </c>
       <c r="G11" s="60" t="s">
-        <v>296</v>
+        <v>452</v>
       </c>
       <c r="I11" s="63"/>
       <c r="J11" s="64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K11" s="64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L11" s="64" t="s">
         <v>57</v>
@@ -7518,14 +7514,14 @@
         <v>57</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="Q11" s="63"/>
       <c r="R11" s="64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S11" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T11" s="64" t="s">
         <v>57</v>
@@ -7537,16 +7533,16 @@
         <v>57</v>
       </c>
       <c r="W11" s="60" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B12" s="63"/>
       <c r="C12" s="64" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E12" s="64" t="s">
         <v>57</v>
@@ -7555,14 +7551,14 @@
         <v>57</v>
       </c>
       <c r="G12" s="60" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I12" s="63"/>
       <c r="J12" s="64" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K12" s="64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L12" s="64" t="s">
         <v>57</v>
@@ -7574,14 +7570,14 @@
         <v>57</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="Q12" s="63"/>
       <c r="R12" s="64" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S12" s="64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T12" s="64" t="s">
         <v>57</v>
@@ -7593,32 +7589,30 @@
         <v>57</v>
       </c>
       <c r="W12" s="60" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B13" s="63"/>
-      <c r="C13" s="64" t="s">
-        <v>358</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>282</v>
-      </c>
-      <c r="E13" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="60" t="s">
-        <v>246</v>
-      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="33"/>
       <c r="I13" s="67"/>
       <c r="J13" s="66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K13" s="66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L13" s="66" t="s">
         <v>57</v>
@@ -7630,14 +7624,14 @@
         <v>57</v>
       </c>
       <c r="O13" s="61" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q13" s="32"/>
       <c r="R13" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="S13" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T13" s="30" t="s">
         <v>57</v>
@@ -7653,10 +7647,10 @@
     <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B14" s="32"/>
       <c r="C14" s="30" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E14" s="30" t="s">
         <v>57</v>
@@ -7667,10 +7661,10 @@
       <c r="G14" s="33"/>
       <c r="I14" s="67"/>
       <c r="J14" s="66" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K14" s="66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L14" s="66" t="s">
         <v>57</v>
@@ -7682,14 +7676,14 @@
         <v>57</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Q14" s="32"/>
       <c r="R14" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S14" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T14" s="30" t="s">
         <v>57</v>
@@ -7705,10 +7699,10 @@
     <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B15" s="32"/>
       <c r="C15" s="30" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E15" s="30" t="s">
         <v>57</v>
@@ -7719,10 +7713,10 @@
       <c r="G15" s="33"/>
       <c r="I15" s="67"/>
       <c r="J15" s="66" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K15" s="66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L15" s="66" t="s">
         <v>57</v>
@@ -7734,14 +7728,14 @@
         <v>57</v>
       </c>
       <c r="O15" s="61" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Q15" s="32"/>
       <c r="R15" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S15" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T15" s="30" t="s">
         <v>57</v>
@@ -7759,10 +7753,10 @@
       <c r="G16" s="33"/>
       <c r="I16" s="67"/>
       <c r="J16" s="66" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K16" s="66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L16" s="66" t="s">
         <v>57</v>
@@ -7774,14 +7768,14 @@
         <v>57</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q16" s="32"/>
       <c r="R16" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T16" s="30" t="s">
         <v>57</v>
@@ -7796,29 +7790,29 @@
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B17" s="63" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D17" s="64" t="s">
         <v>57</v>
       </c>
       <c r="E17" s="64" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F17" s="64" t="s">
         <v>57</v>
       </c>
       <c r="G17" s="60" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I17" s="67"/>
       <c r="J17" s="66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K17" s="66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L17" s="66" t="s">
         <v>57</v>
@@ -7830,14 +7824,14 @@
         <v>57</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q17" s="32"/>
       <c r="R17" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T17" s="30" t="s">
         <v>57</v>
@@ -7853,26 +7847,26 @@
     <row r="18" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B18" s="63"/>
       <c r="C18" s="64" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D18" s="64" t="s">
         <v>57</v>
       </c>
       <c r="E18" s="64" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F18" s="64" t="s">
         <v>57</v>
       </c>
       <c r="G18" s="60" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I18" s="32"/>
       <c r="J18" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L18" s="30" t="s">
         <v>57</v>
@@ -7886,10 +7880,10 @@
       <c r="O18" s="33"/>
       <c r="Q18" s="32"/>
       <c r="R18" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S18" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T18" s="30" t="s">
         <v>57</v>
@@ -7905,13 +7899,13 @@
     <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" s="32"/>
       <c r="C19" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D19" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>57</v>
@@ -7919,10 +7913,10 @@
       <c r="G19" s="33"/>
       <c r="I19" s="32"/>
       <c r="J19" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L19" s="30" t="s">
         <v>57</v>
@@ -7936,10 +7930,10 @@
       <c r="O19" s="33"/>
       <c r="Q19" s="32"/>
       <c r="R19" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S19" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T19" s="30" t="s">
         <v>57</v>
@@ -7955,13 +7949,13 @@
     <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B20" s="32"/>
       <c r="C20" s="30" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D20" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F20" s="30" t="s">
         <v>57</v>
@@ -7969,10 +7963,10 @@
       <c r="G20" s="33"/>
       <c r="I20" s="32"/>
       <c r="J20" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L20" s="30" t="s">
         <v>57</v>
@@ -7986,10 +7980,10 @@
       <c r="O20" s="33"/>
       <c r="Q20" s="32"/>
       <c r="R20" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T20" s="30" t="s">
         <v>57</v>
@@ -8005,13 +7999,13 @@
     <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" s="32"/>
       <c r="C21" s="30" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D21" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F21" s="30" t="s">
         <v>57</v>
@@ -8025,26 +8019,26 @@
     <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" s="32"/>
       <c r="C22" s="30" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D22" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>57</v>
       </c>
       <c r="G22" s="33"/>
       <c r="I22" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J22" s="64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K22" s="64" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L22" s="64" t="s">
         <v>61</v>
@@ -8056,16 +8050,16 @@
         <v>57</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="Q22" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R22" s="64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S22" s="64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T22" s="64" t="s">
         <v>61</v>
@@ -8077,19 +8071,19 @@
         <v>57</v>
       </c>
       <c r="W22" s="60" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" s="32"/>
       <c r="C23" s="30" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D23" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F23" s="30" t="s">
         <v>57</v>
@@ -8097,10 +8091,10 @@
       <c r="G23" s="33"/>
       <c r="I23" s="63"/>
       <c r="J23" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K23" s="64" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L23" s="64" t="s">
         <v>61</v>
@@ -8112,14 +8106,14 @@
         <v>57</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q23" s="63"/>
       <c r="R23" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S23" s="64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T23" s="64" t="s">
         <v>61</v>
@@ -8131,19 +8125,19 @@
         <v>57</v>
       </c>
       <c r="W23" s="60" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B24" s="39"/>
       <c r="C24" s="40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D24" s="40" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F24" s="40" t="s">
         <v>57</v>
@@ -8151,10 +8145,10 @@
       <c r="G24" s="41"/>
       <c r="I24" s="32"/>
       <c r="J24" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L24" s="30" t="s">
         <v>61</v>
@@ -8168,10 +8162,10 @@
       <c r="O24" s="33"/>
       <c r="Q24" s="32"/>
       <c r="R24" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="S24" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T24" s="30" t="s">
         <v>61</v>
@@ -8187,10 +8181,10 @@
     <row r="25" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I25" s="32"/>
       <c r="J25" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L25" s="30" t="s">
         <v>61</v>
@@ -8204,10 +8198,10 @@
       <c r="O25" s="33"/>
       <c r="Q25" s="32"/>
       <c r="R25" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T25" s="30" t="s">
         <v>61</v>
@@ -8223,10 +8217,10 @@
     <row r="26" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I26" s="32"/>
       <c r="J26" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L26" s="30" t="s">
         <v>61</v>
@@ -8240,10 +8234,10 @@
       <c r="O26" s="33"/>
       <c r="Q26" s="32"/>
       <c r="R26" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="S26" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T26" s="30" t="s">
         <v>61</v>
@@ -8259,10 +8253,10 @@
     <row r="27" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I27" s="32"/>
       <c r="J27" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K27" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L27" s="30" t="s">
         <v>61</v>
@@ -8276,10 +8270,10 @@
       <c r="O27" s="33"/>
       <c r="Q27" s="32"/>
       <c r="R27" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="S27" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T27" s="30" t="s">
         <v>61</v>
@@ -8294,14 +8288,14 @@
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B28" s="30" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I28" s="32"/>
       <c r="J28" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K28" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>61</v>
@@ -8315,10 +8309,10 @@
       <c r="O28" s="33"/>
       <c r="Q28" s="32"/>
       <c r="R28" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S28" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T28" s="30" t="s">
         <v>61</v>
@@ -8348,14 +8342,14 @@
         <v>59</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L29" s="30" t="s">
         <v>61</v>
@@ -8369,10 +8363,10 @@
       <c r="O29" s="33"/>
       <c r="Q29" s="32"/>
       <c r="R29" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S29" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T29" s="30" t="s">
         <v>61</v>
@@ -8387,13 +8381,13 @@
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B30" s="63" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E30" s="64" t="s">
         <v>61</v>
@@ -8402,14 +8396,14 @@
         <v>57</v>
       </c>
       <c r="G30" s="60" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I30" s="32"/>
       <c r="J30" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K30" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L30" s="30" t="s">
         <v>61</v>
@@ -8423,10 +8417,10 @@
       <c r="O30" s="33"/>
       <c r="Q30" s="32"/>
       <c r="R30" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="S30" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T30" s="30" t="s">
         <v>61</v>
@@ -8442,10 +8436,10 @@
     <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B31" s="63"/>
       <c r="C31" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D31" s="64" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E31" s="64" t="s">
         <v>61</v>
@@ -8454,14 +8448,14 @@
         <v>57</v>
       </c>
       <c r="G31" s="60" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L31" s="30" t="s">
         <v>61</v>
@@ -8475,10 +8469,10 @@
       <c r="O31" s="33"/>
       <c r="Q31" s="32"/>
       <c r="R31" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S31" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T31" s="30" t="s">
         <v>61</v>
@@ -8494,10 +8488,10 @@
     <row r="32" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B32" s="63"/>
       <c r="C32" s="64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D32" s="64" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E32" s="64" t="s">
         <v>61</v>
@@ -8506,14 +8500,14 @@
         <v>57</v>
       </c>
       <c r="G32" s="60" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I32" s="32"/>
       <c r="J32" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K32" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L32" s="30" t="s">
         <v>61</v>
@@ -8527,10 +8521,10 @@
       <c r="O32" s="33"/>
       <c r="Q32" s="32"/>
       <c r="R32" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S32" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T32" s="30" t="s">
         <v>61</v>
@@ -8546,10 +8540,10 @@
     <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B33" s="63"/>
       <c r="C33" s="64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D33" s="64" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E33" s="64" t="s">
         <v>61</v>
@@ -8558,14 +8552,14 @@
         <v>57</v>
       </c>
       <c r="G33" s="60" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K33" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L33" s="30" t="s">
         <v>61</v>
@@ -8579,10 +8573,10 @@
       <c r="O33" s="33"/>
       <c r="Q33" s="32"/>
       <c r="R33" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S33" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T33" s="30" t="s">
         <v>61</v>
@@ -8598,10 +8592,10 @@
     <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B34" s="32"/>
       <c r="C34" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E34" s="30" t="s">
         <v>61</v>
@@ -8612,10 +8606,10 @@
       <c r="G34" s="33"/>
       <c r="I34" s="32"/>
       <c r="J34" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K34" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L34" s="30" t="s">
         <v>61</v>
@@ -8629,10 +8623,10 @@
       <c r="O34" s="33"/>
       <c r="Q34" s="32"/>
       <c r="R34" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S34" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T34" s="30" t="s">
         <v>61</v>
@@ -8648,10 +8642,10 @@
     <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B35" s="32"/>
       <c r="C35" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E35" s="30" t="s">
         <v>61</v>
@@ -8662,10 +8656,10 @@
       <c r="G35" s="33"/>
       <c r="I35" s="32"/>
       <c r="J35" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K35" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L35" s="30" t="s">
         <v>61</v>
@@ -8679,10 +8673,10 @@
       <c r="O35" s="33"/>
       <c r="Q35" s="32"/>
       <c r="R35" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S35" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T35" s="30" t="s">
         <v>61</v>
@@ -8698,10 +8692,10 @@
     <row r="36" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B36" s="32"/>
       <c r="C36" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E36" s="30" t="s">
         <v>61</v>
@@ -8712,10 +8706,10 @@
       <c r="G36" s="33"/>
       <c r="I36" s="32"/>
       <c r="J36" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K36" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L36" s="30" t="s">
         <v>61</v>
@@ -8729,10 +8723,10 @@
       <c r="O36" s="33"/>
       <c r="Q36" s="32"/>
       <c r="R36" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S36" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T36" s="30" t="s">
         <v>61</v>
@@ -8748,10 +8742,10 @@
     <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="32"/>
       <c r="C37" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>61</v>
@@ -8762,10 +8756,10 @@
       <c r="G37" s="33"/>
       <c r="I37" s="32"/>
       <c r="J37" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L37" s="30" t="s">
         <v>61</v>
@@ -8779,10 +8773,10 @@
       <c r="O37" s="33"/>
       <c r="Q37" s="32"/>
       <c r="R37" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S37" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T37" s="30" t="s">
         <v>61</v>
@@ -8798,10 +8792,10 @@
     <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B38" s="32"/>
       <c r="C38" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E38" s="30" t="s">
         <v>61</v>
@@ -8818,10 +8812,10 @@
     <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B39" s="32"/>
       <c r="C39" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>61</v>
@@ -8831,55 +8825,55 @@
       </c>
       <c r="G39" s="33"/>
       <c r="I39" s="63" t="s">
+        <v>260</v>
+      </c>
+      <c r="J39" s="64" t="s">
         <v>261</v>
       </c>
-      <c r="J39" s="64" t="s">
-        <v>262</v>
-      </c>
       <c r="K39" s="64" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L39" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M39" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N39" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O39" s="60" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Q39" s="63" t="s">
+        <v>260</v>
+      </c>
+      <c r="R39" s="64" t="s">
         <v>261</v>
       </c>
-      <c r="R39" s="64" t="s">
-        <v>262</v>
-      </c>
       <c r="S39" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T39" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U39" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V39" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W39" s="60" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B40" s="32"/>
       <c r="C40" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E40" s="30" t="s">
         <v>61</v>
@@ -8890,50 +8884,50 @@
       <c r="G40" s="33"/>
       <c r="I40" s="63"/>
       <c r="J40" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K40" s="64" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L40" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M40" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N40" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q40" s="63"/>
       <c r="R40" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S40" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T40" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U40" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V40" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W40" s="60" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B41" s="32"/>
       <c r="C41" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E41" s="30" t="s">
         <v>61</v>
@@ -8944,50 +8938,50 @@
       <c r="G41" s="33"/>
       <c r="I41" s="63"/>
       <c r="J41" s="64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K41" s="64" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L41" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M41" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N41" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O41" s="60" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Q41" s="63"/>
       <c r="R41" s="64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="S41" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T41" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U41" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V41" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W41" s="60" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B42" s="32"/>
       <c r="C42" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E42" s="30" t="s">
         <v>61</v>
@@ -8998,50 +8992,50 @@
       <c r="G42" s="33"/>
       <c r="I42" s="63"/>
       <c r="J42" s="64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K42" s="64" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L42" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M42" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N42" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q42" s="63"/>
       <c r="R42" s="64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S42" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T42" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U42" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V42" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W42" s="60" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B43" s="32"/>
       <c r="C43" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E43" s="30" t="s">
         <v>61</v>
@@ -9052,50 +9046,50 @@
       <c r="G43" s="33"/>
       <c r="I43" s="68"/>
       <c r="J43" s="65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K43" s="65" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L43" s="65" t="s">
         <v>61</v>
       </c>
       <c r="M43" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N43" s="65" t="s">
         <v>57</v>
       </c>
       <c r="O43" s="62" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="Q43" s="63"/>
       <c r="R43" s="64" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="S43" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T43" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U43" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V43" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W43" s="60" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B44" s="32"/>
       <c r="C44" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E44" s="30" t="s">
         <v>61</v>
@@ -9106,50 +9100,50 @@
       <c r="G44" s="33"/>
       <c r="I44" s="68"/>
       <c r="J44" s="65" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K44" s="65" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L44" s="65" t="s">
         <v>61</v>
       </c>
       <c r="M44" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N44" s="65" t="s">
         <v>57</v>
       </c>
       <c r="O44" s="62" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q44" s="63"/>
       <c r="R44" s="64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="S44" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T44" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U44" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V44" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W44" s="60" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B45" s="32"/>
       <c r="C45" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E45" s="30" t="s">
         <v>61</v>
@@ -9160,16 +9154,16 @@
       <c r="G45" s="33"/>
       <c r="I45" s="32"/>
       <c r="J45" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K45" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L45" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M45" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N45" s="30" t="s">
         <v>57</v>
@@ -9177,22 +9171,22 @@
       <c r="O45" s="33"/>
       <c r="Q45" s="63"/>
       <c r="R45" s="64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S45" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T45" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U45" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V45" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W45" s="60" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" spans="2:23" x14ac:dyDescent="0.2">
@@ -9200,16 +9194,16 @@
       <c r="G46" s="33"/>
       <c r="I46" s="32"/>
       <c r="J46" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K46" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L46" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M46" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N46" s="30" t="s">
         <v>57</v>
@@ -9217,55 +9211,55 @@
       <c r="O46" s="33"/>
       <c r="Q46" s="63"/>
       <c r="R46" s="64" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S46" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T46" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U46" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V46" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W46" s="60" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B47" s="63" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D47" s="65" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E47" s="64" t="s">
         <v>61</v>
       </c>
       <c r="F47" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G47" s="60" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I47" s="32"/>
       <c r="J47" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K47" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L47" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M47" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N47" s="30" t="s">
         <v>57</v>
@@ -9273,53 +9267,53 @@
       <c r="O47" s="33"/>
       <c r="Q47" s="63"/>
       <c r="R47" s="64" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="S47" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T47" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U47" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V47" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W47" s="60" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B48" s="67"/>
       <c r="C48" s="66" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E48" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F48" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G48" s="61" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K48" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L48" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M48" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N48" s="30" t="s">
         <v>57</v>
@@ -9327,53 +9321,53 @@
       <c r="O48" s="33"/>
       <c r="Q48" s="63"/>
       <c r="R48" s="64" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S48" s="64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T48" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U48" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V48" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W48" s="60" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B49" s="67"/>
       <c r="C49" s="66" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D49" s="66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E49" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F49" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G49" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I49" s="32"/>
       <c r="J49" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K49" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L49" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M49" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N49" s="30" t="s">
         <v>57</v>
@@ -9381,53 +9375,53 @@
       <c r="O49" s="33"/>
       <c r="Q49" s="68"/>
       <c r="R49" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S49" s="65" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T49" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U49" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V49" s="65" t="s">
         <v>57</v>
       </c>
       <c r="W49" s="62" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B50" s="67"/>
       <c r="C50" s="66" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E50" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F50" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G50" s="61" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I50" s="32"/>
       <c r="J50" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K50" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L50" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M50" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N50" s="30" t="s">
         <v>57</v>
@@ -9435,53 +9429,53 @@
       <c r="O50" s="33"/>
       <c r="Q50" s="68"/>
       <c r="R50" s="65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S50" s="65" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T50" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U50" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V50" s="65" t="s">
         <v>57</v>
       </c>
       <c r="W50" s="62" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B51" s="67"/>
       <c r="C51" s="66" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D51" s="66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E51" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F51" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G51" s="61" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I51" s="32"/>
       <c r="J51" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K51" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L51" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M51" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N51" s="30" t="s">
         <v>57</v>
@@ -9489,53 +9483,53 @@
       <c r="O51" s="33"/>
       <c r="Q51" s="67"/>
       <c r="R51" s="66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T51" s="66" t="s">
         <v>61</v>
       </c>
       <c r="U51" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V51" s="66" t="s">
         <v>57</v>
       </c>
       <c r="W51" s="61" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B52" s="63"/>
       <c r="C52" s="64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D52" s="65" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E52" s="64" t="s">
         <v>61</v>
       </c>
       <c r="F52" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G52" s="60" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L52" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M52" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N52" s="30" t="s">
         <v>57</v>
@@ -9543,53 +9537,53 @@
       <c r="O52" s="33"/>
       <c r="Q52" s="67"/>
       <c r="R52" s="66" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T52" s="66" t="s">
         <v>61</v>
       </c>
       <c r="U52" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V52" s="66" t="s">
         <v>57</v>
       </c>
       <c r="W52" s="61" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D53" s="65" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E53" s="64" t="s">
         <v>61</v>
       </c>
       <c r="F53" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G53" s="60" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I53" s="32"/>
       <c r="J53" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K53" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L53" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M53" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N53" s="30" t="s">
         <v>57</v>
@@ -9597,16 +9591,16 @@
       <c r="O53" s="33"/>
       <c r="Q53" s="32"/>
       <c r="R53" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S53" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T53" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U53" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V53" s="30" t="s">
         <v>57</v>
@@ -9616,32 +9610,32 @@
     <row r="54" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B54" s="67"/>
       <c r="C54" s="66" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D54" s="66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E54" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F54" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G54" s="61" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I54" s="32"/>
       <c r="J54" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K54" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L54" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M54" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N54" s="30" t="s">
         <v>57</v>
@@ -9649,16 +9643,16 @@
       <c r="O54" s="33"/>
       <c r="Q54" s="32"/>
       <c r="R54" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S54" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T54" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U54" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V54" s="30" t="s">
         <v>57</v>
@@ -9668,19 +9662,19 @@
     <row r="55" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B55" s="67"/>
       <c r="C55" s="66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D55" s="66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E55" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F55" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G55" s="61" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I55" s="32"/>
       <c r="O55" s="33"/>
@@ -9690,7 +9684,7 @@
     <row r="56" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B56" s="32"/>
       <c r="C56" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>57</v>
@@ -9699,56 +9693,56 @@
         <v>61</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G56" s="33"/>
       <c r="I56" s="63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J56" s="64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K56" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L56" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M56" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N56" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N56" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O56" s="60" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Q56" s="68" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R56" s="65" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S56" s="65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T56" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U56" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="V56" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="V56" s="65" t="s">
-        <v>290</v>
-      </c>
       <c r="W56" s="62" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B57" s="32"/>
       <c r="C57" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D57" s="30" t="s">
         <v>57</v>
@@ -9757,52 +9751,52 @@
         <v>61</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G57" s="33"/>
       <c r="I57" s="63"/>
       <c r="J57" s="64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K57" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L57" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M57" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N57" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N57" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O57" s="60" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q57" s="68"/>
       <c r="R57" s="65" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S57" s="65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T57" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U57" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="V57" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="V57" s="65" t="s">
-        <v>290</v>
-      </c>
       <c r="W57" s="62" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B58" s="32"/>
       <c r="C58" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D58" s="30" t="s">
         <v>57</v>
@@ -9811,52 +9805,52 @@
         <v>61</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G58" s="33"/>
       <c r="I58" s="63"/>
       <c r="J58" s="64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K58" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L58" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M58" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N58" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N58" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O58" s="60" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Q58" s="68"/>
       <c r="R58" s="65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="S58" s="65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T58" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U58" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="V58" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="V58" s="65" t="s">
-        <v>290</v>
-      </c>
       <c r="W58" s="62" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B59" s="32"/>
       <c r="C59" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>57</v>
@@ -9865,52 +9859,52 @@
         <v>61</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G59" s="33"/>
       <c r="I59" s="63"/>
       <c r="J59" s="64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K59" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L59" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M59" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N59" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N59" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O59" s="60" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q59" s="68"/>
       <c r="R59" s="65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S59" s="65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T59" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U59" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="V59" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="V59" s="65" t="s">
-        <v>290</v>
-      </c>
       <c r="W59" s="62" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B60" s="32"/>
       <c r="C60" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D60" s="30" t="s">
         <v>57</v>
@@ -9919,52 +9913,52 @@
         <v>61</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G60" s="33"/>
       <c r="I60" s="63"/>
       <c r="J60" s="64" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K60" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L60" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M60" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N60" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N60" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O60" s="60" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q60" s="68"/>
       <c r="R60" s="65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="S60" s="65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T60" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U60" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="V60" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="V60" s="65" t="s">
-        <v>290</v>
-      </c>
       <c r="W60" s="62" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B61" s="32"/>
       <c r="C61" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D61" s="30" t="s">
         <v>57</v>
@@ -9973,50 +9967,50 @@
         <v>61</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G61" s="33"/>
       <c r="I61" s="63"/>
       <c r="J61" s="64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K61" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L61" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M61" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N61" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N61" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O61" s="60" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q61" s="32"/>
       <c r="R61" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="S61" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T61" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U61" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V61" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V61" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W61" s="33"/>
     </row>
     <row r="62" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B62" s="39"/>
       <c r="C62" s="40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D62" s="40" t="s">
         <v>57</v>
@@ -10025,381 +10019,381 @@
         <v>61</v>
       </c>
       <c r="F62" s="40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G62" s="41"/>
       <c r="I62" s="63"/>
       <c r="J62" s="64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K62" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L62" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M62" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N62" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N62" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O62" s="60" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Q62" s="32"/>
       <c r="R62" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S62" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T62" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U62" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V62" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V62" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W62" s="33"/>
     </row>
     <row r="63" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I63" s="63"/>
       <c r="J63" s="64" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K63" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L63" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M63" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N63" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N63" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O63" s="60" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Q63" s="32"/>
       <c r="R63" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S63" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T63" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U63" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V63" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V63" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W63" s="33"/>
     </row>
     <row r="64" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I64" s="63"/>
       <c r="J64" s="64" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K64" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L64" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M64" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N64" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N64" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O64" s="60" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="Q64" s="32"/>
       <c r="R64" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="S64" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T64" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U64" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V64" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V64" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W64" s="33"/>
     </row>
     <row r="65" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I65" s="63"/>
       <c r="J65" s="64" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K65" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L65" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M65" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N65" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N65" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O65" s="60" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Q65" s="32"/>
       <c r="R65" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S65" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T65" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U65" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V65" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V65" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W65" s="33"/>
     </row>
     <row r="66" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I66" s="63"/>
       <c r="J66" s="64" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K66" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L66" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M66" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N66" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N66" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O66" s="60" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q66" s="32"/>
       <c r="R66" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S66" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T66" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U66" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V66" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V66" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W66" s="33"/>
     </row>
     <row r="67" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I67" s="63"/>
       <c r="J67" s="64" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K67" s="64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L67" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M67" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N67" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N67" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O67" s="60" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q67" s="32"/>
       <c r="R67" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S67" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T67" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U67" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V67" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V67" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W67" s="33"/>
     </row>
     <row r="68" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I68" s="63"/>
       <c r="J68" s="64" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K68" s="65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L68" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M68" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N68" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N68" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O68" s="60" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Q68" s="32"/>
       <c r="R68" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S68" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T68" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U68" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V68" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V68" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W68" s="33"/>
     </row>
     <row r="69" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I69" s="63"/>
       <c r="J69" s="64" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K69" s="65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L69" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M69" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="N69" s="64" t="s">
         <v>289</v>
       </c>
-      <c r="N69" s="64" t="s">
-        <v>290</v>
-      </c>
       <c r="O69" s="60" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q69" s="32"/>
       <c r="R69" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S69" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T69" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U69" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V69" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V69" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W69" s="33"/>
     </row>
     <row r="70" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I70" s="32"/>
       <c r="J70" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K70" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L70" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M70" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="N70" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="N70" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="O70" s="33"/>
       <c r="Q70" s="32"/>
       <c r="R70" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S70" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T70" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U70" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="V70" s="30" t="s">
         <v>289</v>
-      </c>
-      <c r="V70" s="30" t="s">
-        <v>290</v>
       </c>
       <c r="W70" s="33"/>
     </row>
     <row r="71" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I71" s="39"/>
       <c r="J71" s="40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K71" s="40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L71" s="40" t="s">
         <v>61</v>
       </c>
       <c r="M71" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="N71" s="40" t="s">
         <v>289</v>
-      </c>
-      <c r="N71" s="40" t="s">
-        <v>290</v>
       </c>
       <c r="O71" s="41"/>
       <c r="Q71" s="39"/>
       <c r="R71" s="40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S71" s="40" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T71" s="40" t="s">
         <v>61</v>
       </c>
       <c r="U71" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="V71" s="40" t="s">
         <v>289</v>
-      </c>
-      <c r="V71" s="40" t="s">
-        <v>290</v>
       </c>
       <c r="W71" s="41"/>
     </row>

--- a/RiscISAv1.1 .xlsx
+++ b/RiscISAv1.1 .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79849496-652C-414E-8799-FB13120F6BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983551BD-0098-4128-AEB5-A720D5F1C830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="454" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="454" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruction format" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="447">
   <si>
     <t>bit0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -701,14 +701,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CSR#1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CSR#2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CBR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -733,10 +725,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CSR#3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1538,10 +1526,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CSR#0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bit31</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1558,10 +1542,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CSR#4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>IE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1590,10 +1570,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CSR#5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SPR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1630,10 +1606,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CSR#3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>STTR/SPTR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1735,6 +1707,10 @@
   </si>
   <si>
     <t>scall.mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2172,7 +2148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2332,6 +2308,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3047,7 +3024,7 @@
     </row>
     <row r="18" spans="2:25" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="43" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="44"/>
@@ -3064,7 +3041,7 @@
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>50</v>
@@ -3073,10 +3050,10 @@
         <v>49</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.2">
@@ -3142,7 +3119,7 @@
       <c r="D22" s="44"/>
       <c r="E22" s="44"/>
       <c r="F22" s="42" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G22" s="42" t="s">
         <v>131</v>
@@ -3206,7 +3183,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="K24" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>51</v>
@@ -3218,13 +3195,13 @@
         <v>49</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.2">
@@ -3308,49 +3285,49 @@
     </row>
     <row r="27" spans="2:25" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="F27" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="G27" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="E27" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>241</v>
-      </c>
       <c r="H27" s="42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J27" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="L27" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="M27" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="N27" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="O27" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="P27" s="42" t="s">
         <v>225</v>
-      </c>
-      <c r="K27" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="L27" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="M27" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="N27" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="O27" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="P27" s="42" t="s">
-        <v>228</v>
       </c>
       <c r="Q27" s="29"/>
       <c r="R27" s="14"/>
@@ -3380,34 +3357,34 @@
       <c r="D28" s="44"/>
       <c r="E28" s="44"/>
       <c r="F28" s="42" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H28" s="42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I28" s="42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K28" s="42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L28" s="42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="M28" s="42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N28" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O28" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P28" s="42" t="s">
         <v>128</v>
@@ -3440,22 +3417,22 @@
       <c r="H29" s="46"/>
       <c r="I29" s="46"/>
       <c r="J29" s="42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K29" s="42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L29" s="42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="M29" s="42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N29" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O29" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P29" s="42" t="s">
         <v>128</v>
@@ -3494,10 +3471,10 @@
       <c r="L30" s="48"/>
       <c r="M30" s="48"/>
       <c r="N30" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O30" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P30" s="42" t="s">
         <v>128</v>
@@ -3536,10 +3513,10 @@
       <c r="L31" s="48"/>
       <c r="M31" s="48"/>
       <c r="N31" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O31" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P31" s="42" t="s">
         <v>128</v>
@@ -3571,31 +3548,31 @@
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="T32" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="R32" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="S32" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="T32" s="8" t="s">
-        <v>320</v>
-      </c>
       <c r="U32" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="V32" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="W32" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="V32" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="W32" s="8" t="s">
-        <v>319</v>
-      </c>
       <c r="X32" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.2">
@@ -3703,70 +3680,70 @@
     </row>
     <row r="35" spans="2:33" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="F35" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="G35" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="E35" s="42" t="s">
+      <c r="H35" s="42" t="s">
         <v>232</v>
       </c>
-      <c r="F35" s="42" t="s">
+      <c r="I35" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="G35" s="42" t="s">
+      <c r="J35" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="H35" s="42" t="s">
+      <c r="K35" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="I35" s="42" t="s">
+      <c r="L35" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="J35" s="42" t="s">
+      <c r="M35" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="K35" s="42" t="s">
+      <c r="N35" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="L35" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="M35" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="N35" s="42" t="s">
-        <v>241</v>
-      </c>
       <c r="O35" s="42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P35" s="42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q35" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="R35" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="S35" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="T35" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="U35" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="V35" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="W35" s="42" t="s">
         <v>225</v>
-      </c>
-      <c r="R35" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="S35" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="T35" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="U35" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="V35" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="W35" s="42" t="s">
-        <v>228</v>
       </c>
       <c r="X35" s="29"/>
       <c r="Y35" s="14"/>
@@ -3799,55 +3776,55 @@
       <c r="D36" s="44"/>
       <c r="E36" s="44"/>
       <c r="F36" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="H36" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="I36" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="G36" s="42" t="s">
+      <c r="J36" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="H36" s="42" t="s">
+      <c r="K36" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="I36" s="42" t="s">
+      <c r="L36" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="J36" s="42" t="s">
+      <c r="M36" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="K36" s="42" t="s">
+      <c r="N36" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="L36" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="M36" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="N36" s="42" t="s">
-        <v>241</v>
-      </c>
       <c r="O36" s="42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P36" s="42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q36" s="42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="R36" s="42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S36" s="42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T36" s="42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="U36" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="V36" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="W36" s="42" t="s">
         <v>128</v>
@@ -3881,43 +3858,43 @@
       <c r="H37" s="46"/>
       <c r="I37" s="46"/>
       <c r="J37" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="L37" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="M37" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="K37" s="42" t="s">
+      <c r="N37" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="L37" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="M37" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="N37" s="42" t="s">
-        <v>241</v>
-      </c>
       <c r="O37" s="42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P37" s="42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q37" s="42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="R37" s="42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S37" s="42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T37" s="42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="U37" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="V37" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="W37" s="42" t="s">
         <v>128</v>
@@ -3957,31 +3934,31 @@
       <c r="L38" s="48"/>
       <c r="M38" s="48"/>
       <c r="N38" s="42" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O38" s="42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P38" s="42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q38" s="42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="R38" s="42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S38" s="42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T38" s="42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="U38" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="V38" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="W38" s="42" t="s">
         <v>128</v>
@@ -4021,31 +3998,31 @@
       <c r="L39" s="48"/>
       <c r="M39" s="48"/>
       <c r="N39" s="42" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O39" s="42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P39" s="42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q39" s="42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="R39" s="42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S39" s="42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T39" s="42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="U39" s="42" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="V39" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="W39" s="42" t="s">
         <v>128</v>
@@ -4085,34 +4062,34 @@
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="Y40" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="Z40" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="AA40" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="Y40" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="Z40" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="AA40" s="8" t="s">
+      <c r="AB40" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="AC40" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD40" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="AB40" s="8" t="s">
+      <c r="AE40" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="AC40" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD40" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="AE40" s="8" t="s">
-        <v>319</v>
-      </c>
       <c r="AF40" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG40" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -4137,13 +4114,13 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="51" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D2" s="54" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -4159,7 +4136,7 @@
         <v>132</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>127</v>
@@ -4240,10 +4217,10 @@
         <v>68</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>68</v>
@@ -4254,10 +4231,10 @@
         <v>69</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E13" s="50" t="s">
         <v>69</v>
@@ -4268,10 +4245,10 @@
         <v>70</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E14" s="50" t="s">
         <v>70</v>
@@ -4282,7 +4259,7 @@
         <v>71</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>87</v>
@@ -4296,13 +4273,13 @@
         <v>72</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>88</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F16" s="49"/>
       <c r="G16" s="49"/>
@@ -4312,13 +4289,13 @@
         <v>73</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F17" s="49"/>
       <c r="G17" s="49"/>
@@ -4328,13 +4305,13 @@
         <v>74</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D18" s="34" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F18" s="49"/>
       <c r="G18" s="49"/>
@@ -4350,7 +4327,7 @@
         <v>95</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F19" s="49"/>
       <c r="G19" s="49"/>
@@ -4374,7 +4351,7 @@
         <v>77</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D21" s="34" t="s">
         <v>98</v>
@@ -4388,7 +4365,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D22" s="34" t="s">
         <v>97</v>
@@ -4443,10 +4420,10 @@
         <v>100</v>
       </c>
       <c r="F30" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G30" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
@@ -4463,10 +4440,10 @@
         <v>101</v>
       </c>
       <c r="F31" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G31" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
@@ -4483,10 +4460,10 @@
         <v>102</v>
       </c>
       <c r="F32" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G32" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
@@ -4503,10 +4480,10 @@
         <v>103</v>
       </c>
       <c r="F33" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G33" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
@@ -4523,10 +4500,10 @@
         <v>104</v>
       </c>
       <c r="F34" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G34" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
@@ -4534,19 +4511,19 @@
         <v>105</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E35" s="53" t="s">
         <v>105</v>
       </c>
       <c r="F35" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G35" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
@@ -4554,19 +4531,19 @@
         <v>106</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F36" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G36" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
@@ -4574,19 +4551,19 @@
         <v>107</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F37" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G37" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
@@ -4594,19 +4571,19 @@
         <v>108</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D38" s="34" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F38" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G38" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
@@ -4614,19 +4591,19 @@
         <v>109</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D39" s="34" t="s">
         <v>140</v>
       </c>
       <c r="E39" s="53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F39" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G39" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
@@ -4640,13 +4617,13 @@
         <v>141</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G40" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
@@ -4660,13 +4637,13 @@
         <v>142</v>
       </c>
       <c r="E41" s="53" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G41" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
@@ -4680,13 +4657,13 @@
         <v>143</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F42" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G42" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
@@ -4703,10 +4680,10 @@
         <v>113</v>
       </c>
       <c r="F43" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G43" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
@@ -4717,16 +4694,16 @@
         <v>125</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E44" s="53" t="s">
         <v>114</v>
       </c>
       <c r="F44" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G44" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
@@ -4737,16 +4714,16 @@
         <v>126</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E45" s="53" t="s">
         <v>115</v>
       </c>
       <c r="F45" s="69" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G45" s="69" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4765,18 +4742,18 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="34" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="34" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -4853,34 +4830,34 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="71" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G14" s="70" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="71" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G15" s="70" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="71" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G16" s="70" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="71" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G17" s="70" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -4928,19 +4905,19 @@
         <v>100</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D27" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G27" s="71" t="s">
         <v>100</v>
       </c>
       <c r="H27" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I27" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -4948,19 +4925,19 @@
         <v>101</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G28" s="71" t="s">
         <v>101</v>
       </c>
       <c r="H28" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I28" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -4968,19 +4945,19 @@
         <v>102</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G29" s="71" t="s">
         <v>102</v>
       </c>
       <c r="H29" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I29" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -4988,19 +4965,19 @@
         <v>103</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D30" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G30" s="71" t="s">
         <v>103</v>
       </c>
       <c r="H30" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I30" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -5008,19 +4985,19 @@
         <v>104</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D31" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G31" s="71" t="s">
         <v>104</v>
       </c>
       <c r="H31" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I31" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -5028,159 +5005,159 @@
         <v>105</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D32" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G32" s="71" t="s">
         <v>105</v>
       </c>
       <c r="H32" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I32" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="71" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D33" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G33" s="71" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H33" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I33" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34" s="71" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C34" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D34" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G34" s="71" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H34" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I34" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35" s="71" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C35" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D35" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G35" s="70" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H35" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I35" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" s="71" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C36" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D36" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G36" s="70" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H36" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I36" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37" s="71" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C37" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D37" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G37" s="70" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H37" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I37" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="71" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C38" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G38" s="70" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H38" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I38" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B39" s="71" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C39" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D39" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G39" s="70" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H39" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I39" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
@@ -5188,19 +5165,19 @@
         <v>113</v>
       </c>
       <c r="C40" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D40" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G40" s="70" t="s">
         <v>113</v>
       </c>
       <c r="H40" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I40" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
@@ -5208,19 +5185,19 @@
         <v>114</v>
       </c>
       <c r="C41" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D41" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G41" s="70" t="s">
         <v>114</v>
       </c>
       <c r="H41" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I41" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.2">
@@ -5228,19 +5205,19 @@
         <v>115</v>
       </c>
       <c r="C42" s="72" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D42" s="72" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G42" s="70" t="s">
         <v>115</v>
       </c>
       <c r="H42" s="73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I42" s="73" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -5251,7 +5228,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C21CFC4-0250-4D09-827E-BEDDE4D8F3AE}">
-  <dimension ref="A2:AG60"/>
+  <dimension ref="A2:AG71"/>
   <sheetFormatPr defaultColWidth="6.25" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="6.25" style="34"/>
@@ -5452,24 +5429,24 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>184</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>40</v>
@@ -5632,24 +5609,24 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="34" t="s">
-        <v>187</v>
+        <v>446</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>40</v>
@@ -5773,21 +5750,21 @@
       <c r="AC15" s="75"/>
       <c r="AD15" s="75"/>
       <c r="AE15" s="35" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AF15" s="35" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AG15" s="35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B16" s="34" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.2">
@@ -5821,35 +5798,35 @@
       <c r="AC17" s="75"/>
       <c r="AD17" s="75"/>
       <c r="AE17" s="35" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AF17" s="35" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AG17" s="35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="34" t="s">
-        <v>188</v>
+        <v>446</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D20" s="34" t="s">
         <v>40</v>
@@ -6012,10 +5989,10 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B23" s="34" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.2">
@@ -6088,24 +6065,24 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D28" s="34" t="s">
         <v>40</v>
@@ -6268,10 +6245,10 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B31" s="34" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.2">
@@ -6344,7 +6321,7 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="34" t="s">
-        <v>188</v>
+        <v>446</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>184</v>
@@ -6494,7 +6471,7 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A39" s="34" t="s">
-        <v>195</v>
+        <v>446</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>185</v>
@@ -6635,7 +6612,7 @@
       <c r="AC41" s="37"/>
       <c r="AD41" s="37"/>
       <c r="AE41" s="35" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AF41" s="36" t="s">
         <v>179</v>
@@ -6644,7 +6621,7 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A43" s="34" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>183</v>
@@ -6824,18 +6801,18 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A48" s="34" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>25</v>
@@ -7003,52 +6980,896 @@
       <c r="AG51" s="38"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A53" s="34" t="s">
+        <v>446</v>
+      </c>
       <c r="B53" s="34" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B54" s="34" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>411</v>
+        <v>39</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I54" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J54" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L54" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M54" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N54" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="O54" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="P54" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q54" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="R54" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S54" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="T54" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="U54" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="V54" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="W54" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X54" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y54" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z54" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB54" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD54" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE54" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG54" s="34" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B55" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>412</v>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="37"/>
+      <c r="I55" s="37"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="37"/>
+      <c r="L55" s="37"/>
+      <c r="M55" s="37"/>
+      <c r="N55" s="37"/>
+      <c r="O55" s="37"/>
+      <c r="P55" s="37"/>
+      <c r="Q55" s="37"/>
+      <c r="R55" s="37"/>
+      <c r="S55" s="37"/>
+      <c r="T55" s="37"/>
+      <c r="U55" s="37"/>
+      <c r="V55" s="37"/>
+      <c r="W55" s="37"/>
+      <c r="X55" s="37"/>
+      <c r="Y55" s="37"/>
+      <c r="Z55" s="37"/>
+      <c r="AA55" s="37"/>
+      <c r="AB55" s="37"/>
+      <c r="AC55" s="37"/>
+      <c r="AD55" s="37"/>
+      <c r="AE55" s="37"/>
+      <c r="AF55" s="37"/>
+      <c r="AG55" s="38"/>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A56" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B57" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F57" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H57" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I57" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J57" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L57" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N57" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="O57" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="P57" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q57" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="R57" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S57" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="T57" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="U57" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="V57" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="W57" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X57" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y57" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z57" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD57" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE57" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG57" s="34" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B58" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C58" s="34" t="s">
-        <v>413</v>
-      </c>
+      <c r="B58" s="36"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+      <c r="I58" s="37"/>
+      <c r="J58" s="37"/>
+      <c r="K58" s="37"/>
+      <c r="L58" s="37"/>
+      <c r="M58" s="37"/>
+      <c r="N58" s="37"/>
+      <c r="O58" s="37"/>
+      <c r="P58" s="37"/>
+      <c r="Q58" s="37"/>
+      <c r="R58" s="37"/>
+      <c r="S58" s="37"/>
+      <c r="T58" s="37"/>
+      <c r="U58" s="37"/>
+      <c r="V58" s="37"/>
+      <c r="W58" s="37"/>
+      <c r="X58" s="37"/>
+      <c r="Y58" s="37"/>
+      <c r="Z58" s="37"/>
+      <c r="AA58" s="37"/>
+      <c r="AB58" s="37"/>
+      <c r="AC58" s="37"/>
+      <c r="AD58" s="37"/>
+      <c r="AE58" s="37"/>
+      <c r="AF58" s="37"/>
+      <c r="AG58" s="38"/>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A59" s="34" t="s">
+        <v>446</v>
+      </c>
       <c r="B59" s="34" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B60" s="34" t="s">
-        <v>191</v>
+        <v>25</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>415</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H60" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I60" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J60" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K60" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M60" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N60" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="O60" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="P60" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q60" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="R60" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S60" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="T60" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="U60" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="V60" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="W60" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X60" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y60" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z60" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB60" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD60" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE60" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG60" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B61" s="36"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="37"/>
+      <c r="I61" s="37"/>
+      <c r="J61" s="37"/>
+      <c r="K61" s="37"/>
+      <c r="L61" s="37"/>
+      <c r="M61" s="37"/>
+      <c r="N61" s="37"/>
+      <c r="O61" s="37"/>
+      <c r="P61" s="37"/>
+      <c r="Q61" s="37"/>
+      <c r="R61" s="37"/>
+      <c r="S61" s="37"/>
+      <c r="T61" s="37"/>
+      <c r="U61" s="37"/>
+      <c r="V61" s="37"/>
+      <c r="W61" s="37"/>
+      <c r="X61" s="37"/>
+      <c r="Y61" s="37"/>
+      <c r="Z61" s="37"/>
+      <c r="AA61" s="37"/>
+      <c r="AB61" s="37"/>
+      <c r="AC61" s="37"/>
+      <c r="AD61" s="37"/>
+      <c r="AE61" s="37"/>
+      <c r="AF61" s="37"/>
+      <c r="AG61" s="38"/>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="77"/>
+      <c r="E62" s="77"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="77"/>
+      <c r="I62" s="77"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="77"/>
+      <c r="M62" s="77"/>
+      <c r="N62" s="77"/>
+      <c r="O62" s="77"/>
+      <c r="P62" s="77"/>
+      <c r="Q62" s="77"/>
+      <c r="R62" s="77"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="77"/>
+      <c r="U62" s="77"/>
+      <c r="V62" s="77"/>
+      <c r="W62" s="77"/>
+      <c r="X62" s="77"/>
+      <c r="Y62" s="77"/>
+      <c r="Z62" s="77"/>
+      <c r="AA62" s="77"/>
+      <c r="AB62" s="77"/>
+      <c r="AC62" s="77"/>
+      <c r="AD62" s="77"/>
+      <c r="AE62" s="77"/>
+      <c r="AF62" s="77"/>
+      <c r="AG62" s="77"/>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A63" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="B63" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B64" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E64" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I64" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J64" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K64" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L64" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M64" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N64" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="O64" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="P64" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q64" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="R64" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S64" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="T64" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="U64" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="V64" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="W64" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X64" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y64" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z64" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA64" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB64" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC64" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD64" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE64" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG64" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B65" s="36"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="37"/>
+      <c r="J65" s="37"/>
+      <c r="K65" s="37"/>
+      <c r="L65" s="37"/>
+      <c r="M65" s="37"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="37"/>
+      <c r="R65" s="37"/>
+      <c r="S65" s="37"/>
+      <c r="T65" s="37"/>
+      <c r="U65" s="37"/>
+      <c r="V65" s="37"/>
+      <c r="W65" s="37"/>
+      <c r="X65" s="37"/>
+      <c r="Y65" s="37"/>
+      <c r="Z65" s="37"/>
+      <c r="AA65" s="37"/>
+      <c r="AB65" s="37"/>
+      <c r="AC65" s="37"/>
+      <c r="AD65" s="37"/>
+      <c r="AE65" s="37"/>
+      <c r="AF65" s="37"/>
+      <c r="AG65" s="38"/>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A66" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B67" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E67" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H67" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I67" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J67" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K67" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L67" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M67" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N67" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="O67" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="P67" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q67" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="R67" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S67" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="T67" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="U67" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="V67" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="W67" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X67" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y67" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z67" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA67" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB67" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC67" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD67" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE67" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG67" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B68" s="36"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="37"/>
+      <c r="K68" s="37"/>
+      <c r="L68" s="37"/>
+      <c r="M68" s="37"/>
+      <c r="N68" s="37"/>
+      <c r="O68" s="37"/>
+      <c r="P68" s="37"/>
+      <c r="Q68" s="37"/>
+      <c r="R68" s="37"/>
+      <c r="S68" s="37"/>
+      <c r="T68" s="37"/>
+      <c r="U68" s="37"/>
+      <c r="V68" s="37"/>
+      <c r="W68" s="37"/>
+      <c r="X68" s="37"/>
+      <c r="Y68" s="37"/>
+      <c r="Z68" s="37"/>
+      <c r="AA68" s="37"/>
+      <c r="AB68" s="37"/>
+      <c r="AC68" s="37"/>
+      <c r="AD68" s="37"/>
+      <c r="AE68" s="37"/>
+      <c r="AF68" s="37"/>
+      <c r="AG68" s="38"/>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A69" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B70" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F70" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H70" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I70" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J70" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L70" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M70" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N70" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="O70" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="P70" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q70" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="R70" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S70" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="T70" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="U70" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="V70" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="W70" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X70" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y70" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z70" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA70" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB70" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC70" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD70" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE70" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG70" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B71" s="36"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="37"/>
+      <c r="I71" s="37"/>
+      <c r="J71" s="37"/>
+      <c r="K71" s="37"/>
+      <c r="L71" s="37"/>
+      <c r="M71" s="37"/>
+      <c r="N71" s="37"/>
+      <c r="O71" s="37"/>
+      <c r="P71" s="37"/>
+      <c r="Q71" s="37"/>
+      <c r="R71" s="37"/>
+      <c r="S71" s="37"/>
+      <c r="T71" s="37"/>
+      <c r="U71" s="37"/>
+      <c r="V71" s="37"/>
+      <c r="W71" s="37"/>
+      <c r="X71" s="37"/>
+      <c r="Y71" s="37"/>
+      <c r="Z71" s="37"/>
+      <c r="AA71" s="37"/>
+      <c r="AB71" s="37"/>
+      <c r="AC71" s="37"/>
+      <c r="AD71" s="37"/>
+      <c r="AE71" s="37"/>
+      <c r="AF71" s="37"/>
+      <c r="AG71" s="38"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7078,30 +7899,30 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I2" s="30" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q2" s="30" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B3" s="64" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D3" s="65" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J3" s="59" t="s">
         <v>60</v>
       </c>
       <c r="K3" s="57" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L3" s="59" t="s">
         <v>58</v>
@@ -7110,19 +7931,19 @@
         <v>59</v>
       </c>
       <c r="N3" s="59" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="O3" s="58" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q3" s="56" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="R3" s="59" t="s">
         <v>60</v>
       </c>
       <c r="S3" s="57" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="T3" s="59" t="s">
         <v>58</v>
@@ -7131,10 +7952,10 @@
         <v>59</v>
       </c>
       <c r="V3" s="59" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="W3" s="58" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="2:23" x14ac:dyDescent="0.2">
@@ -7142,26 +7963,26 @@
       <c r="J4" s="55"/>
       <c r="K4" s="40"/>
       <c r="L4" s="55" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="N4" s="55" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O4" s="41"/>
       <c r="Q4" s="39"/>
       <c r="R4" s="55"/>
       <c r="S4" s="40"/>
       <c r="T4" s="55" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="V4" s="55" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="W4" s="41"/>
     </row>
@@ -7170,10 +7991,10 @@
         <v>56</v>
       </c>
       <c r="J5" s="64" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K5" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L5" s="64" t="s">
         <v>57</v>
@@ -7185,16 +8006,16 @@
         <v>57</v>
       </c>
       <c r="O5" s="60" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q5" s="63" t="s">
         <v>56</v>
       </c>
       <c r="R5" s="64" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="S5" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T5" s="64" t="s">
         <v>57</v>
@@ -7206,19 +8027,19 @@
         <v>57</v>
       </c>
       <c r="W5" s="60" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B6" s="30" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I6" s="63"/>
       <c r="J6" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K6" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L6" s="64" t="s">
         <v>57</v>
@@ -7230,14 +8051,14 @@
         <v>57</v>
       </c>
       <c r="O6" s="60" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Q6" s="63"/>
       <c r="R6" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="S6" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T6" s="64" t="s">
         <v>57</v>
@@ -7249,34 +8070,34 @@
         <v>57</v>
       </c>
       <c r="W6" s="60" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B7" s="31" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>60</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E7" s="31" t="s">
         <v>58</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I7" s="63"/>
       <c r="J7" s="64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K7" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L7" s="64" t="s">
         <v>57</v>
@@ -7288,14 +8109,14 @@
         <v>57</v>
       </c>
       <c r="O7" s="60" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q7" s="63"/>
       <c r="R7" s="64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="S7" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T7" s="64" t="s">
         <v>57</v>
@@ -7307,18 +8128,18 @@
         <v>57</v>
       </c>
       <c r="W7" s="60" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B8" s="63" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D8" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E8" s="64" t="s">
         <v>57</v>
@@ -7327,14 +8148,14 @@
         <v>57</v>
       </c>
       <c r="G8" s="60" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I8" s="63"/>
       <c r="J8" s="64" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K8" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L8" s="64" t="s">
         <v>57</v>
@@ -7346,14 +8167,14 @@
         <v>57</v>
       </c>
       <c r="O8" s="60" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q8" s="63"/>
       <c r="R8" s="64" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="S8" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T8" s="64" t="s">
         <v>57</v>
@@ -7365,16 +8186,16 @@
         <v>57</v>
       </c>
       <c r="W8" s="60" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B9" s="63"/>
       <c r="C9" s="64" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E9" s="64" t="s">
         <v>57</v>
@@ -7383,14 +8204,14 @@
         <v>57</v>
       </c>
       <c r="G9" s="60" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I9" s="63"/>
       <c r="J9" s="64" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K9" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L9" s="64" t="s">
         <v>57</v>
@@ -7402,14 +8223,14 @@
         <v>57</v>
       </c>
       <c r="O9" s="60" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="Q9" s="63"/>
       <c r="R9" s="64" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="S9" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T9" s="64" t="s">
         <v>57</v>
@@ -7421,16 +8242,16 @@
         <v>57</v>
       </c>
       <c r="W9" s="60" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B10" s="63"/>
       <c r="C10" s="64" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E10" s="64" t="s">
         <v>57</v>
@@ -7439,14 +8260,14 @@
         <v>57</v>
       </c>
       <c r="G10" s="60" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I10" s="63"/>
       <c r="J10" s="64" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K10" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L10" s="64" t="s">
         <v>57</v>
@@ -7458,14 +8279,14 @@
         <v>57</v>
       </c>
       <c r="O10" s="60" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q10" s="63"/>
       <c r="R10" s="64" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="S10" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T10" s="64" t="s">
         <v>57</v>
@@ -7477,16 +8298,16 @@
         <v>57</v>
       </c>
       <c r="W10" s="60" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B11" s="63"/>
       <c r="C11" s="64" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D11" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E11" s="64" t="s">
         <v>57</v>
@@ -7495,14 +8316,14 @@
         <v>57</v>
       </c>
       <c r="G11" s="60" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="I11" s="63"/>
       <c r="J11" s="64" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K11" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L11" s="64" t="s">
         <v>57</v>
@@ -7514,14 +8335,14 @@
         <v>57</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Q11" s="63"/>
       <c r="R11" s="64" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="S11" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T11" s="64" t="s">
         <v>57</v>
@@ -7533,16 +8354,16 @@
         <v>57</v>
       </c>
       <c r="W11" s="60" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B12" s="63"/>
       <c r="C12" s="64" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E12" s="64" t="s">
         <v>57</v>
@@ -7551,14 +8372,14 @@
         <v>57</v>
       </c>
       <c r="G12" s="60" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I12" s="63"/>
       <c r="J12" s="64" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K12" s="64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L12" s="64" t="s">
         <v>57</v>
@@ -7570,14 +8391,14 @@
         <v>57</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q12" s="63"/>
       <c r="R12" s="64" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S12" s="64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T12" s="64" t="s">
         <v>57</v>
@@ -7589,16 +8410,16 @@
         <v>57</v>
       </c>
       <c r="W12" s="60" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B13" s="32"/>
       <c r="C13" s="30" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E13" s="30" t="s">
         <v>57</v>
@@ -7609,10 +8430,10 @@
       <c r="G13" s="33"/>
       <c r="I13" s="67"/>
       <c r="J13" s="66" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K13" s="66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L13" s="66" t="s">
         <v>57</v>
@@ -7624,14 +8445,14 @@
         <v>57</v>
       </c>
       <c r="O13" s="61" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="Q13" s="32"/>
       <c r="R13" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="S13" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T13" s="30" t="s">
         <v>57</v>
@@ -7647,10 +8468,10 @@
     <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B14" s="32"/>
       <c r="C14" s="30" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E14" s="30" t="s">
         <v>57</v>
@@ -7661,10 +8482,10 @@
       <c r="G14" s="33"/>
       <c r="I14" s="67"/>
       <c r="J14" s="66" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K14" s="66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L14" s="66" t="s">
         <v>57</v>
@@ -7676,14 +8497,14 @@
         <v>57</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="Q14" s="32"/>
       <c r="R14" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="S14" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T14" s="30" t="s">
         <v>57</v>
@@ -7699,10 +8520,10 @@
     <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B15" s="32"/>
       <c r="C15" s="30" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E15" s="30" t="s">
         <v>57</v>
@@ -7713,10 +8534,10 @@
       <c r="G15" s="33"/>
       <c r="I15" s="67"/>
       <c r="J15" s="66" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K15" s="66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L15" s="66" t="s">
         <v>57</v>
@@ -7728,14 +8549,14 @@
         <v>57</v>
       </c>
       <c r="O15" s="61" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="Q15" s="32"/>
       <c r="R15" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="S15" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T15" s="30" t="s">
         <v>57</v>
@@ -7753,10 +8574,10 @@
       <c r="G16" s="33"/>
       <c r="I16" s="67"/>
       <c r="J16" s="66" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K16" s="66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L16" s="66" t="s">
         <v>57</v>
@@ -7768,14 +8589,14 @@
         <v>57</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="Q16" s="32"/>
       <c r="R16" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T16" s="30" t="s">
         <v>57</v>
@@ -7790,29 +8611,29 @@
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B17" s="63" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D17" s="64" t="s">
         <v>57</v>
       </c>
       <c r="E17" s="64" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F17" s="64" t="s">
         <v>57</v>
       </c>
       <c r="G17" s="60" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I17" s="67"/>
       <c r="J17" s="66" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K17" s="66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L17" s="66" t="s">
         <v>57</v>
@@ -7824,14 +8645,14 @@
         <v>57</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="Q17" s="32"/>
       <c r="R17" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T17" s="30" t="s">
         <v>57</v>
@@ -7847,26 +8668,26 @@
     <row r="18" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B18" s="63"/>
       <c r="C18" s="64" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D18" s="64" t="s">
         <v>57</v>
       </c>
       <c r="E18" s="64" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F18" s="64" t="s">
         <v>57</v>
       </c>
       <c r="G18" s="60" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I18" s="32"/>
       <c r="J18" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L18" s="30" t="s">
         <v>57</v>
@@ -7880,10 +8701,10 @@
       <c r="O18" s="33"/>
       <c r="Q18" s="32"/>
       <c r="R18" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="S18" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T18" s="30" t="s">
         <v>57</v>
@@ -7899,13 +8720,13 @@
     <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" s="32"/>
       <c r="C19" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D19" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>57</v>
@@ -7913,10 +8734,10 @@
       <c r="G19" s="33"/>
       <c r="I19" s="32"/>
       <c r="J19" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L19" s="30" t="s">
         <v>57</v>
@@ -7930,10 +8751,10 @@
       <c r="O19" s="33"/>
       <c r="Q19" s="32"/>
       <c r="R19" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="S19" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T19" s="30" t="s">
         <v>57</v>
@@ -7949,13 +8770,13 @@
     <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B20" s="32"/>
       <c r="C20" s="30" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D20" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F20" s="30" t="s">
         <v>57</v>
@@ -7963,10 +8784,10 @@
       <c r="G20" s="33"/>
       <c r="I20" s="32"/>
       <c r="J20" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L20" s="30" t="s">
         <v>57</v>
@@ -7980,10 +8801,10 @@
       <c r="O20" s="33"/>
       <c r="Q20" s="32"/>
       <c r="R20" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T20" s="30" t="s">
         <v>57</v>
@@ -7999,13 +8820,13 @@
     <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" s="32"/>
       <c r="C21" s="30" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D21" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F21" s="30" t="s">
         <v>57</v>
@@ -8019,26 +8840,26 @@
     <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" s="32"/>
       <c r="C22" s="30" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D22" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>57</v>
       </c>
       <c r="G22" s="33"/>
       <c r="I22" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="J22" s="64" t="s">
         <v>258</v>
       </c>
-      <c r="J22" s="64" t="s">
-        <v>261</v>
-      </c>
       <c r="K22" s="64" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L22" s="64" t="s">
         <v>61</v>
@@ -8050,16 +8871,16 @@
         <v>57</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q22" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="R22" s="64" t="s">
         <v>258</v>
       </c>
-      <c r="R22" s="64" t="s">
-        <v>261</v>
-      </c>
       <c r="S22" s="64" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T22" s="64" t="s">
         <v>61</v>
@@ -8071,19 +8892,19 @@
         <v>57</v>
       </c>
       <c r="W22" s="60" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" s="32"/>
       <c r="C23" s="30" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D23" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F23" s="30" t="s">
         <v>57</v>
@@ -8091,10 +8912,10 @@
       <c r="G23" s="33"/>
       <c r="I23" s="63"/>
       <c r="J23" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K23" s="64" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L23" s="64" t="s">
         <v>61</v>
@@ -8106,14 +8927,14 @@
         <v>57</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q23" s="63"/>
       <c r="R23" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="S23" s="64" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T23" s="64" t="s">
         <v>61</v>
@@ -8125,19 +8946,19 @@
         <v>57</v>
       </c>
       <c r="W23" s="60" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B24" s="39"/>
       <c r="C24" s="40" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D24" s="40" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F24" s="40" t="s">
         <v>57</v>
@@ -8145,10 +8966,10 @@
       <c r="G24" s="41"/>
       <c r="I24" s="32"/>
       <c r="J24" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L24" s="30" t="s">
         <v>61</v>
@@ -8162,10 +8983,10 @@
       <c r="O24" s="33"/>
       <c r="Q24" s="32"/>
       <c r="R24" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="S24" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T24" s="30" t="s">
         <v>61</v>
@@ -8181,10 +9002,10 @@
     <row r="25" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I25" s="32"/>
       <c r="J25" s="30" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L25" s="30" t="s">
         <v>61</v>
@@ -8198,10 +9019,10 @@
       <c r="O25" s="33"/>
       <c r="Q25" s="32"/>
       <c r="R25" s="30" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T25" s="30" t="s">
         <v>61</v>
@@ -8217,10 +9038,10 @@
     <row r="26" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I26" s="32"/>
       <c r="J26" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L26" s="30" t="s">
         <v>61</v>
@@ -8234,10 +9055,10 @@
       <c r="O26" s="33"/>
       <c r="Q26" s="32"/>
       <c r="R26" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="S26" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T26" s="30" t="s">
         <v>61</v>
@@ -8253,10 +9074,10 @@
     <row r="27" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I27" s="32"/>
       <c r="J27" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K27" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L27" s="30" t="s">
         <v>61</v>
@@ -8270,10 +9091,10 @@
       <c r="O27" s="33"/>
       <c r="Q27" s="32"/>
       <c r="R27" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="S27" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T27" s="30" t="s">
         <v>61</v>
@@ -8288,14 +9109,14 @@
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B28" s="30" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I28" s="32"/>
       <c r="J28" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K28" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>61</v>
@@ -8309,10 +9130,10 @@
       <c r="O28" s="33"/>
       <c r="Q28" s="32"/>
       <c r="R28" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="S28" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T28" s="30" t="s">
         <v>61</v>
@@ -8327,13 +9148,13 @@
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B29" s="31" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>60</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E29" s="31" t="s">
         <v>58</v>
@@ -8342,14 +9163,14 @@
         <v>59</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L29" s="30" t="s">
         <v>61</v>
@@ -8363,10 +9184,10 @@
       <c r="O29" s="33"/>
       <c r="Q29" s="32"/>
       <c r="R29" s="30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S29" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T29" s="30" t="s">
         <v>61</v>
@@ -8381,13 +9202,13 @@
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B30" s="63" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E30" s="64" t="s">
         <v>61</v>
@@ -8396,14 +9217,14 @@
         <v>57</v>
       </c>
       <c r="G30" s="60" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I30" s="32"/>
       <c r="J30" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K30" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L30" s="30" t="s">
         <v>61</v>
@@ -8417,10 +9238,10 @@
       <c r="O30" s="33"/>
       <c r="Q30" s="32"/>
       <c r="R30" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="S30" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T30" s="30" t="s">
         <v>61</v>
@@ -8436,10 +9257,10 @@
     <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B31" s="63"/>
       <c r="C31" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D31" s="64" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E31" s="64" t="s">
         <v>61</v>
@@ -8448,14 +9269,14 @@
         <v>57</v>
       </c>
       <c r="G31" s="60" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L31" s="30" t="s">
         <v>61</v>
@@ -8469,10 +9290,10 @@
       <c r="O31" s="33"/>
       <c r="Q31" s="32"/>
       <c r="R31" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="S31" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T31" s="30" t="s">
         <v>61</v>
@@ -8488,10 +9309,10 @@
     <row r="32" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B32" s="63"/>
       <c r="C32" s="64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D32" s="64" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E32" s="64" t="s">
         <v>61</v>
@@ -8500,14 +9321,14 @@
         <v>57</v>
       </c>
       <c r="G32" s="60" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I32" s="32"/>
       <c r="J32" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K32" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L32" s="30" t="s">
         <v>61</v>
@@ -8521,10 +9342,10 @@
       <c r="O32" s="33"/>
       <c r="Q32" s="32"/>
       <c r="R32" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="S32" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T32" s="30" t="s">
         <v>61</v>
@@ -8540,10 +9361,10 @@
     <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B33" s="63"/>
       <c r="C33" s="64" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D33" s="64" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E33" s="64" t="s">
         <v>61</v>
@@ -8552,14 +9373,14 @@
         <v>57</v>
       </c>
       <c r="G33" s="60" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K33" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L33" s="30" t="s">
         <v>61</v>
@@ -8573,10 +9394,10 @@
       <c r="O33" s="33"/>
       <c r="Q33" s="32"/>
       <c r="R33" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S33" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T33" s="30" t="s">
         <v>61</v>
@@ -8592,10 +9413,10 @@
     <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B34" s="32"/>
       <c r="C34" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E34" s="30" t="s">
         <v>61</v>
@@ -8606,10 +9427,10 @@
       <c r="G34" s="33"/>
       <c r="I34" s="32"/>
       <c r="J34" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K34" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L34" s="30" t="s">
         <v>61</v>
@@ -8623,10 +9444,10 @@
       <c r="O34" s="33"/>
       <c r="Q34" s="32"/>
       <c r="R34" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="S34" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T34" s="30" t="s">
         <v>61</v>
@@ -8642,10 +9463,10 @@
     <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B35" s="32"/>
       <c r="C35" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E35" s="30" t="s">
         <v>61</v>
@@ -8656,10 +9477,10 @@
       <c r="G35" s="33"/>
       <c r="I35" s="32"/>
       <c r="J35" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K35" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L35" s="30" t="s">
         <v>61</v>
@@ -8673,10 +9494,10 @@
       <c r="O35" s="33"/>
       <c r="Q35" s="32"/>
       <c r="R35" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="S35" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T35" s="30" t="s">
         <v>61</v>
@@ -8692,10 +9513,10 @@
     <row r="36" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B36" s="32"/>
       <c r="C36" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E36" s="30" t="s">
         <v>61</v>
@@ -8706,10 +9527,10 @@
       <c r="G36" s="33"/>
       <c r="I36" s="32"/>
       <c r="J36" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="K36" s="30" t="s">
         <v>276</v>
-      </c>
-      <c r="K36" s="30" t="s">
-        <v>279</v>
       </c>
       <c r="L36" s="30" t="s">
         <v>61</v>
@@ -8723,10 +9544,10 @@
       <c r="O36" s="33"/>
       <c r="Q36" s="32"/>
       <c r="R36" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="S36" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T36" s="30" t="s">
         <v>61</v>
@@ -8742,10 +9563,10 @@
     <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="32"/>
       <c r="C37" s="30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>61</v>
@@ -8756,10 +9577,10 @@
       <c r="G37" s="33"/>
       <c r="I37" s="32"/>
       <c r="J37" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L37" s="30" t="s">
         <v>61</v>
@@ -8773,10 +9594,10 @@
       <c r="O37" s="33"/>
       <c r="Q37" s="32"/>
       <c r="R37" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="S37" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T37" s="30" t="s">
         <v>61</v>
@@ -8792,10 +9613,10 @@
     <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B38" s="32"/>
       <c r="C38" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E38" s="30" t="s">
         <v>61</v>
@@ -8812,10 +9633,10 @@
     <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B39" s="32"/>
       <c r="C39" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>61</v>
@@ -8825,55 +9646,55 @@
       </c>
       <c r="G39" s="33"/>
       <c r="I39" s="63" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J39" s="64" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K39" s="64" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L39" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M39" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N39" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O39" s="60" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q39" s="63" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R39" s="64" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="S39" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T39" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U39" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V39" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W39" s="60" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B40" s="32"/>
       <c r="C40" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E40" s="30" t="s">
         <v>61</v>
@@ -8884,50 +9705,50 @@
       <c r="G40" s="33"/>
       <c r="I40" s="63"/>
       <c r="J40" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K40" s="64" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L40" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M40" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N40" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q40" s="63"/>
       <c r="R40" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="S40" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T40" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U40" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V40" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W40" s="60" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B41" s="32"/>
       <c r="C41" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E41" s="30" t="s">
         <v>61</v>
@@ -8938,50 +9759,50 @@
       <c r="G41" s="33"/>
       <c r="I41" s="63"/>
       <c r="J41" s="64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K41" s="64" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L41" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M41" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N41" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O41" s="60" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Q41" s="63"/>
       <c r="R41" s="64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="S41" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T41" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U41" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V41" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W41" s="60" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B42" s="32"/>
       <c r="C42" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E42" s="30" t="s">
         <v>61</v>
@@ -8992,50 +9813,50 @@
       <c r="G42" s="33"/>
       <c r="I42" s="63"/>
       <c r="J42" s="64" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K42" s="64" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L42" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M42" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N42" s="64" t="s">
         <v>57</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="Q42" s="63"/>
       <c r="R42" s="64" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="S42" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T42" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U42" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V42" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W42" s="60" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B43" s="32"/>
       <c r="C43" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E43" s="30" t="s">
         <v>61</v>
@@ -9046,50 +9867,50 @@
       <c r="G43" s="33"/>
       <c r="I43" s="68"/>
       <c r="J43" s="65" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K43" s="65" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L43" s="65" t="s">
         <v>61</v>
       </c>
       <c r="M43" s="65" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N43" s="65" t="s">
         <v>57</v>
       </c>
       <c r="O43" s="62" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="Q43" s="63"/>
       <c r="R43" s="64" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="S43" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T43" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U43" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V43" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W43" s="60" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B44" s="32"/>
       <c r="C44" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E44" s="30" t="s">
         <v>61</v>
@@ -9100,50 +9921,50 @@
       <c r="G44" s="33"/>
       <c r="I44" s="68"/>
       <c r="J44" s="65" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K44" s="65" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L44" s="65" t="s">
         <v>61</v>
       </c>
       <c r="M44" s="65" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N44" s="65" t="s">
         <v>57</v>
       </c>
       <c r="O44" s="62" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="Q44" s="63"/>
       <c r="R44" s="64" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="S44" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T44" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U44" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V44" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W44" s="60" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B45" s="32"/>
       <c r="C45" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E45" s="30" t="s">
         <v>61</v>
@@ -9154,16 +9975,16 @@
       <c r="G45" s="33"/>
       <c r="I45" s="32"/>
       <c r="J45" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K45" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L45" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M45" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N45" s="30" t="s">
         <v>57</v>
@@ -9171,22 +9992,22 @@
       <c r="O45" s="33"/>
       <c r="Q45" s="63"/>
       <c r="R45" s="64" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="S45" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T45" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U45" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V45" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W45" s="60" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="2:23" x14ac:dyDescent="0.2">
@@ -9194,16 +10015,16 @@
       <c r="G46" s="33"/>
       <c r="I46" s="32"/>
       <c r="J46" s="30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K46" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L46" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M46" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N46" s="30" t="s">
         <v>57</v>
@@ -9211,55 +10032,55 @@
       <c r="O46" s="33"/>
       <c r="Q46" s="63"/>
       <c r="R46" s="64" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S46" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T46" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U46" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V46" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W46" s="60" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B47" s="63" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D47" s="65" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E47" s="64" t="s">
         <v>61</v>
       </c>
       <c r="F47" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G47" s="60" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="I47" s="32"/>
       <c r="J47" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K47" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L47" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M47" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N47" s="30" t="s">
         <v>57</v>
@@ -9267,53 +10088,53 @@
       <c r="O47" s="33"/>
       <c r="Q47" s="63"/>
       <c r="R47" s="64" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="S47" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T47" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U47" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V47" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W47" s="60" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B48" s="67"/>
       <c r="C48" s="66" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E48" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F48" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G48" s="61" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K48" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L48" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M48" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N48" s="30" t="s">
         <v>57</v>
@@ -9321,53 +10142,53 @@
       <c r="O48" s="33"/>
       <c r="Q48" s="63"/>
       <c r="R48" s="64" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="S48" s="64" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T48" s="64" t="s">
         <v>61</v>
       </c>
       <c r="U48" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V48" s="64" t="s">
         <v>57</v>
       </c>
       <c r="W48" s="60" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B49" s="67"/>
       <c r="C49" s="66" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D49" s="66" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E49" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F49" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G49" s="61" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="I49" s="32"/>
       <c r="J49" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K49" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L49" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M49" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N49" s="30" t="s">
         <v>57</v>
@@ -9375,53 +10196,53 @@
       <c r="O49" s="33"/>
       <c r="Q49" s="68"/>
       <c r="R49" s="65" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="S49" s="65" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T49" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U49" s="65" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V49" s="65" t="s">
         <v>57</v>
       </c>
       <c r="W49" s="62" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B50" s="67"/>
       <c r="C50" s="66" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E50" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F50" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G50" s="61" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="I50" s="32"/>
       <c r="J50" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K50" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L50" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M50" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N50" s="30" t="s">
         <v>57</v>
@@ -9429,53 +10250,53 @@
       <c r="O50" s="33"/>
       <c r="Q50" s="68"/>
       <c r="R50" s="65" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S50" s="65" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T50" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U50" s="65" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V50" s="65" t="s">
         <v>57</v>
       </c>
       <c r="W50" s="62" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="51" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B51" s="67"/>
       <c r="C51" s="66" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D51" s="66" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E51" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F51" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G51" s="61" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="I51" s="32"/>
       <c r="J51" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K51" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L51" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M51" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N51" s="30" t="s">
         <v>57</v>
@@ -9483,53 +10304,53 @@
       <c r="O51" s="33"/>
       <c r="Q51" s="67"/>
       <c r="R51" s="66" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T51" s="66" t="s">
         <v>61</v>
       </c>
       <c r="U51" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V51" s="66" t="s">
         <v>57</v>
       </c>
       <c r="W51" s="61" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B52" s="63"/>
       <c r="C52" s="64" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D52" s="65" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E52" s="64" t="s">
         <v>61</v>
       </c>
       <c r="F52" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G52" s="60" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L52" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M52" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N52" s="30" t="s">
         <v>57</v>
@@ -9537,53 +10358,53 @@
       <c r="O52" s="33"/>
       <c r="Q52" s="67"/>
       <c r="R52" s="66" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T52" s="66" t="s">
         <v>61</v>
       </c>
       <c r="U52" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V52" s="66" t="s">
         <v>57</v>
       </c>
       <c r="W52" s="61" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D53" s="65" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E53" s="64" t="s">
         <v>61</v>
       </c>
       <c r="F53" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G53" s="60" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="I53" s="32"/>
       <c r="J53" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K53" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L53" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M53" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N53" s="30" t="s">
         <v>57</v>
@@ -9591,16 +10412,16 @@
       <c r="O53" s="33"/>
       <c r="Q53" s="32"/>
       <c r="R53" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="S53" s="30" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T53" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U53" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V53" s="30" t="s">
         <v>57</v>
@@ -9610,32 +10431,32 @@
     <row r="54" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B54" s="67"/>
       <c r="C54" s="66" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D54" s="66" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E54" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F54" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G54" s="61" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I54" s="32"/>
       <c r="J54" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="K54" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="K54" s="30" t="s">
-        <v>280</v>
-      </c>
       <c r="L54" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M54" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N54" s="30" t="s">
         <v>57</v>
@@ -9643,16 +10464,16 @@
       <c r="O54" s="33"/>
       <c r="Q54" s="32"/>
       <c r="R54" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="S54" s="30" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="T54" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U54" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="V54" s="30" t="s">
         <v>57</v>
@@ -9662,19 +10483,19 @@
     <row r="55" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B55" s="67"/>
       <c r="C55" s="66" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D55" s="66" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E55" s="66" t="s">
         <v>61</v>
       </c>
       <c r="F55" s="66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G55" s="61" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I55" s="32"/>
       <c r="O55" s="33"/>
@@ -9684,7 +10505,7 @@
     <row r="56" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B56" s="32"/>
       <c r="C56" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>57</v>
@@ -9693,56 +10514,56 @@
         <v>61</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G56" s="33"/>
       <c r="I56" s="63" t="s">
+        <v>275</v>
+      </c>
+      <c r="J56" s="64" t="s">
+        <v>258</v>
+      </c>
+      <c r="K56" s="64" t="s">
         <v>278</v>
       </c>
-      <c r="J56" s="64" t="s">
-        <v>261</v>
-      </c>
-      <c r="K56" s="64" t="s">
-        <v>281</v>
-      </c>
       <c r="L56" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M56" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N56" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O56" s="60" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q56" s="68" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="R56" s="65" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="S56" s="65" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T56" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U56" s="65" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V56" s="65" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W56" s="62" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="57" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B57" s="32"/>
       <c r="C57" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D57" s="30" t="s">
         <v>57</v>
@@ -9751,52 +10572,52 @@
         <v>61</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G57" s="33"/>
       <c r="I57" s="63"/>
       <c r="J57" s="64" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K57" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L57" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M57" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N57" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O57" s="60" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="Q57" s="68"/>
       <c r="R57" s="65" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="S57" s="65" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T57" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U57" s="65" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V57" s="65" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W57" s="62" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="58" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B58" s="32"/>
       <c r="C58" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D58" s="30" t="s">
         <v>57</v>
@@ -9805,52 +10626,52 @@
         <v>61</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G58" s="33"/>
       <c r="I58" s="63"/>
       <c r="J58" s="64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K58" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L58" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M58" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N58" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O58" s="60" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q58" s="68"/>
       <c r="R58" s="65" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="S58" s="65" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T58" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U58" s="65" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V58" s="65" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W58" s="62" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B59" s="32"/>
       <c r="C59" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>57</v>
@@ -9859,52 +10680,52 @@
         <v>61</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G59" s="33"/>
       <c r="I59" s="63"/>
       <c r="J59" s="64" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K59" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L59" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M59" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N59" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O59" s="60" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="Q59" s="68"/>
       <c r="R59" s="65" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="S59" s="65" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T59" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U59" s="65" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V59" s="65" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W59" s="62" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="60" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B60" s="32"/>
       <c r="C60" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D60" s="30" t="s">
         <v>57</v>
@@ -9913,52 +10734,52 @@
         <v>61</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G60" s="33"/>
       <c r="I60" s="63"/>
       <c r="J60" s="64" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K60" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L60" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M60" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N60" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O60" s="60" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q60" s="68"/>
       <c r="R60" s="65" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="S60" s="65" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T60" s="65" t="s">
         <v>61</v>
       </c>
       <c r="U60" s="65" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V60" s="65" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W60" s="62" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="61" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B61" s="32"/>
       <c r="C61" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D61" s="30" t="s">
         <v>57</v>
@@ -9967,50 +10788,50 @@
         <v>61</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G61" s="33"/>
       <c r="I61" s="63"/>
       <c r="J61" s="64" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K61" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L61" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M61" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N61" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O61" s="60" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Q61" s="32"/>
       <c r="R61" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="S61" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T61" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U61" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V61" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W61" s="33"/>
     </row>
     <row r="62" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B62" s="39"/>
       <c r="C62" s="40" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D62" s="40" t="s">
         <v>57</v>
@@ -10019,381 +10840,381 @@
         <v>61</v>
       </c>
       <c r="F62" s="40" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G62" s="41"/>
       <c r="I62" s="63"/>
       <c r="J62" s="64" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K62" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L62" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M62" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N62" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O62" s="60" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q62" s="32"/>
       <c r="R62" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="S62" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T62" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U62" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V62" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W62" s="33"/>
     </row>
     <row r="63" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I63" s="63"/>
       <c r="J63" s="64" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K63" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L63" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M63" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N63" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O63" s="60" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="Q63" s="32"/>
       <c r="R63" s="30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S63" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T63" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U63" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V63" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W63" s="33"/>
     </row>
     <row r="64" spans="2:23" x14ac:dyDescent="0.2">
       <c r="I64" s="63"/>
       <c r="J64" s="64" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K64" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L64" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M64" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N64" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O64" s="60" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="Q64" s="32"/>
       <c r="R64" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="S64" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T64" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U64" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V64" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W64" s="33"/>
     </row>
     <row r="65" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I65" s="63"/>
       <c r="J65" s="64" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K65" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L65" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M65" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N65" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O65" s="60" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="Q65" s="32"/>
       <c r="R65" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="S65" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T65" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U65" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V65" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W65" s="33"/>
     </row>
     <row r="66" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I66" s="63"/>
       <c r="J66" s="64" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K66" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L66" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M66" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N66" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O66" s="60" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Q66" s="32"/>
       <c r="R66" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="S66" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T66" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U66" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V66" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W66" s="33"/>
     </row>
     <row r="67" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I67" s="63"/>
       <c r="J67" s="64" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K67" s="64" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L67" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M67" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N67" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O67" s="60" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="Q67" s="32"/>
       <c r="R67" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S67" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T67" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U67" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V67" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W67" s="33"/>
     </row>
     <row r="68" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I68" s="63"/>
       <c r="J68" s="64" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K68" s="65" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L68" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M68" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N68" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O68" s="60" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Q68" s="32"/>
       <c r="R68" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="S68" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T68" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U68" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V68" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W68" s="33"/>
     </row>
     <row r="69" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I69" s="63"/>
       <c r="J69" s="64" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K69" s="65" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L69" s="64" t="s">
         <v>61</v>
       </c>
       <c r="M69" s="64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N69" s="64" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O69" s="60" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="Q69" s="32"/>
       <c r="R69" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="S69" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T69" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U69" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V69" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W69" s="33"/>
     </row>
     <row r="70" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I70" s="32"/>
       <c r="J70" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K70" s="30" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L70" s="30" t="s">
         <v>61</v>
       </c>
       <c r="M70" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N70" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O70" s="33"/>
       <c r="Q70" s="32"/>
       <c r="R70" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="S70" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T70" s="30" t="s">
         <v>61</v>
       </c>
       <c r="U70" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V70" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W70" s="33"/>
     </row>
     <row r="71" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I71" s="39"/>
       <c r="J71" s="40" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K71" s="40" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L71" s="40" t="s">
         <v>61</v>
       </c>
       <c r="M71" s="40" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N71" s="40" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O71" s="41"/>
       <c r="Q71" s="39"/>
       <c r="R71" s="40" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="S71" s="40" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T71" s="40" t="s">
         <v>61</v>
       </c>
       <c r="U71" s="40" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V71" s="40" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W71" s="41"/>
     </row>
